--- a/File Research/Game Object Research File.xlsx
+++ b/File Research/Game Object Research File.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5AA285-A41E-44B2-88D7-EB7B46401AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D92536-C625-471A-9C02-0F050BF1CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{349C9796-1BFF-4A71-A28F-BEE29BD20DAE}"/>
   </bookViews>
@@ -776,11 +776,6 @@
 checked when they die</t>
   </si>
   <si>
-    <t>Bit set when creating pit fighter
-Later checked for skipping when spawning npcs.
-References with createobject traps</t>
-  </si>
-  <si>
     <t>In a homing dart/satellite if bit 7 is set projectile hp is set to 0. (hp in this case is ticking down slowly)</t>
   </si>
   <si>
@@ -943,6 +938,11 @@
   </si>
   <si>
     <t>Controls when mobile object is next refreshed</t>
+  </si>
+  <si>
+    <t>Bit set when creating pit fighter
+Later checked for skipping when spawning npcs.
+References with createobject traps. Set on the template object when doing an on map createobject (eg when sleeping)</t>
   </si>
 </sst>
 </file>
@@ -1696,26 +1696,246 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1760,227 +1980,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2423,1075 +2423,1075 @@
       <c r="A1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="122" t="s">
+      <c r="B1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
-      <c r="O1" s="123"/>
-      <c r="P1" s="123"/>
-      <c r="Q1" s="123"/>
-      <c r="R1" s="123"/>
-      <c r="S1" s="123"/>
-      <c r="T1" s="123"/>
-      <c r="U1" s="123"/>
-      <c r="V1" s="123"/>
-      <c r="W1" s="123"/>
-      <c r="X1" s="123"/>
-      <c r="Y1" s="123"/>
-      <c r="Z1" s="123"/>
-      <c r="AA1" s="123"/>
-      <c r="AB1" s="123"/>
-      <c r="AC1" s="123"/>
-      <c r="AD1" s="123"/>
-      <c r="AE1" s="123"/>
-      <c r="AF1" s="123"/>
-      <c r="AG1" s="123"/>
-      <c r="AH1" s="123"/>
-      <c r="AI1" s="123"/>
-      <c r="AJ1" s="123"/>
-      <c r="AK1" s="123"/>
-      <c r="AL1" s="123"/>
-      <c r="AM1" s="123"/>
-      <c r="AN1" s="123"/>
-      <c r="AO1" s="123"/>
-      <c r="AP1" s="123"/>
-      <c r="AQ1" s="123"/>
-      <c r="AR1" s="123"/>
-      <c r="AS1" s="123"/>
-      <c r="AT1" s="123"/>
-      <c r="AU1" s="123"/>
-      <c r="AV1" s="123"/>
-      <c r="AW1" s="123"/>
-      <c r="AX1" s="123"/>
-      <c r="AY1" s="123"/>
-      <c r="AZ1" s="123"/>
-      <c r="BA1" s="123"/>
-      <c r="BB1" s="123"/>
-      <c r="BC1" s="123"/>
-      <c r="BD1" s="123"/>
-      <c r="BE1" s="123"/>
-      <c r="BF1" s="123"/>
-      <c r="BG1" s="123"/>
-      <c r="BH1" s="123"/>
-      <c r="BI1" s="123"/>
-      <c r="BJ1" s="123"/>
-      <c r="BK1" s="123"/>
-      <c r="BL1" s="123"/>
-      <c r="BM1" s="124"/>
-      <c r="BN1" s="122" t="s">
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="81"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="81"/>
+      <c r="AF1" s="81"/>
+      <c r="AG1" s="81"/>
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="81"/>
+      <c r="AO1" s="81"/>
+      <c r="AP1" s="81"/>
+      <c r="AQ1" s="81"/>
+      <c r="AR1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="81"/>
+      <c r="BI1" s="81"/>
+      <c r="BJ1" s="81"/>
+      <c r="BK1" s="81"/>
+      <c r="BL1" s="81"/>
+      <c r="BM1" s="82"/>
+      <c r="BN1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="BO1" s="123"/>
-      <c r="BP1" s="123"/>
-      <c r="BQ1" s="123"/>
-      <c r="BR1" s="123"/>
-      <c r="BS1" s="123"/>
-      <c r="BT1" s="123"/>
-      <c r="BU1" s="123"/>
-      <c r="BV1" s="123"/>
-      <c r="BW1" s="123"/>
-      <c r="BX1" s="123"/>
-      <c r="BY1" s="123"/>
-      <c r="BZ1" s="123"/>
-      <c r="CA1" s="123"/>
-      <c r="CB1" s="123"/>
-      <c r="CC1" s="123"/>
-      <c r="CD1" s="123"/>
-      <c r="CE1" s="123"/>
-      <c r="CF1" s="123"/>
-      <c r="CG1" s="123"/>
-      <c r="CH1" s="123"/>
-      <c r="CI1" s="123"/>
-      <c r="CJ1" s="123"/>
-      <c r="CK1" s="123"/>
-      <c r="CL1" s="123"/>
-      <c r="CM1" s="123"/>
-      <c r="CN1" s="123"/>
-      <c r="CO1" s="123"/>
-      <c r="CP1" s="123"/>
-      <c r="CQ1" s="123"/>
-      <c r="CR1" s="123"/>
-      <c r="CS1" s="123"/>
-      <c r="CT1" s="123"/>
-      <c r="CU1" s="123"/>
-      <c r="CV1" s="123"/>
-      <c r="CW1" s="123"/>
-      <c r="CX1" s="123"/>
-      <c r="CY1" s="123"/>
-      <c r="CZ1" s="123"/>
-      <c r="DA1" s="123"/>
-      <c r="DB1" s="123"/>
-      <c r="DC1" s="123"/>
-      <c r="DD1" s="123"/>
-      <c r="DE1" s="123"/>
-      <c r="DF1" s="123"/>
-      <c r="DG1" s="123"/>
-      <c r="DH1" s="123"/>
-      <c r="DI1" s="123"/>
-      <c r="DJ1" s="123"/>
-      <c r="DK1" s="123"/>
-      <c r="DL1" s="123"/>
-      <c r="DM1" s="123"/>
-      <c r="DN1" s="123"/>
-      <c r="DO1" s="123"/>
-      <c r="DP1" s="123"/>
-      <c r="DQ1" s="123"/>
-      <c r="DR1" s="123"/>
-      <c r="DS1" s="123"/>
-      <c r="DT1" s="123"/>
-      <c r="DU1" s="123"/>
-      <c r="DV1" s="123"/>
-      <c r="DW1" s="123"/>
-      <c r="DX1" s="123"/>
-      <c r="DY1" s="123"/>
-      <c r="DZ1" s="123"/>
-      <c r="EA1" s="123"/>
-      <c r="EB1" s="123"/>
-      <c r="EC1" s="123"/>
-      <c r="ED1" s="123"/>
-      <c r="EE1" s="123"/>
-      <c r="EF1" s="123"/>
-      <c r="EG1" s="123"/>
-      <c r="EH1" s="123"/>
-      <c r="EI1" s="123"/>
-      <c r="EJ1" s="123"/>
-      <c r="EK1" s="123"/>
-      <c r="EL1" s="123"/>
-      <c r="EM1" s="123"/>
-      <c r="EN1" s="123"/>
-      <c r="EO1" s="123"/>
-      <c r="EP1" s="123"/>
-      <c r="EQ1" s="123"/>
-      <c r="ER1" s="123"/>
-      <c r="ES1" s="123"/>
-      <c r="ET1" s="123"/>
-      <c r="EU1" s="123"/>
-      <c r="EV1" s="123"/>
-      <c r="EW1" s="123"/>
-      <c r="EX1" s="123"/>
-      <c r="EY1" s="123"/>
-      <c r="EZ1" s="123"/>
-      <c r="FA1" s="123"/>
-      <c r="FB1" s="123"/>
-      <c r="FC1" s="123"/>
-      <c r="FD1" s="123"/>
-      <c r="FE1" s="123"/>
-      <c r="FF1" s="123"/>
-      <c r="FG1" s="123"/>
-      <c r="FH1" s="123"/>
-      <c r="FI1" s="123"/>
-      <c r="FJ1" s="123"/>
-      <c r="FK1" s="123"/>
-      <c r="FL1" s="123"/>
-      <c r="FM1" s="123"/>
-      <c r="FN1" s="123"/>
-      <c r="FO1" s="123"/>
-      <c r="FP1" s="123"/>
-      <c r="FQ1" s="123"/>
-      <c r="FR1" s="123"/>
-      <c r="FS1" s="123"/>
-      <c r="FT1" s="123"/>
-      <c r="FU1" s="123"/>
-      <c r="FV1" s="123"/>
-      <c r="FW1" s="123"/>
-      <c r="FX1" s="123"/>
-      <c r="FY1" s="123"/>
-      <c r="FZ1" s="123"/>
-      <c r="GA1" s="123"/>
-      <c r="GB1" s="123"/>
-      <c r="GC1" s="123"/>
-      <c r="GD1" s="123"/>
-      <c r="GE1" s="123"/>
-      <c r="GF1" s="123"/>
-      <c r="GG1" s="123"/>
-      <c r="GH1" s="123"/>
-      <c r="GI1" s="123"/>
-      <c r="GJ1" s="123"/>
-      <c r="GK1" s="123"/>
-      <c r="GL1" s="123"/>
-      <c r="GM1" s="123"/>
-      <c r="GN1" s="123"/>
-      <c r="GO1" s="123"/>
-      <c r="GP1" s="123"/>
-      <c r="GQ1" s="123"/>
-      <c r="GR1" s="123"/>
-      <c r="GS1" s="123"/>
-      <c r="GT1" s="123"/>
-      <c r="GU1" s="123"/>
-      <c r="GV1" s="123"/>
-      <c r="GW1" s="123"/>
-      <c r="GX1" s="123"/>
-      <c r="GY1" s="123"/>
-      <c r="GZ1" s="123"/>
-      <c r="HA1" s="123"/>
-      <c r="HB1" s="123"/>
-      <c r="HC1" s="123"/>
-      <c r="HD1" s="123"/>
-      <c r="HE1" s="123"/>
-      <c r="HF1" s="123"/>
-      <c r="HG1" s="123"/>
-      <c r="HH1" s="123"/>
-      <c r="HI1" s="123"/>
+      <c r="BO1" s="81"/>
+      <c r="BP1" s="81"/>
+      <c r="BQ1" s="81"/>
+      <c r="BR1" s="81"/>
+      <c r="BS1" s="81"/>
+      <c r="BT1" s="81"/>
+      <c r="BU1" s="81"/>
+      <c r="BV1" s="81"/>
+      <c r="BW1" s="81"/>
+      <c r="BX1" s="81"/>
+      <c r="BY1" s="81"/>
+      <c r="BZ1" s="81"/>
+      <c r="CA1" s="81"/>
+      <c r="CB1" s="81"/>
+      <c r="CC1" s="81"/>
+      <c r="CD1" s="81"/>
+      <c r="CE1" s="81"/>
+      <c r="CF1" s="81"/>
+      <c r="CG1" s="81"/>
+      <c r="CH1" s="81"/>
+      <c r="CI1" s="81"/>
+      <c r="CJ1" s="81"/>
+      <c r="CK1" s="81"/>
+      <c r="CL1" s="81"/>
+      <c r="CM1" s="81"/>
+      <c r="CN1" s="81"/>
+      <c r="CO1" s="81"/>
+      <c r="CP1" s="81"/>
+      <c r="CQ1" s="81"/>
+      <c r="CR1" s="81"/>
+      <c r="CS1" s="81"/>
+      <c r="CT1" s="81"/>
+      <c r="CU1" s="81"/>
+      <c r="CV1" s="81"/>
+      <c r="CW1" s="81"/>
+      <c r="CX1" s="81"/>
+      <c r="CY1" s="81"/>
+      <c r="CZ1" s="81"/>
+      <c r="DA1" s="81"/>
+      <c r="DB1" s="81"/>
+      <c r="DC1" s="81"/>
+      <c r="DD1" s="81"/>
+      <c r="DE1" s="81"/>
+      <c r="DF1" s="81"/>
+      <c r="DG1" s="81"/>
+      <c r="DH1" s="81"/>
+      <c r="DI1" s="81"/>
+      <c r="DJ1" s="81"/>
+      <c r="DK1" s="81"/>
+      <c r="DL1" s="81"/>
+      <c r="DM1" s="81"/>
+      <c r="DN1" s="81"/>
+      <c r="DO1" s="81"/>
+      <c r="DP1" s="81"/>
+      <c r="DQ1" s="81"/>
+      <c r="DR1" s="81"/>
+      <c r="DS1" s="81"/>
+      <c r="DT1" s="81"/>
+      <c r="DU1" s="81"/>
+      <c r="DV1" s="81"/>
+      <c r="DW1" s="81"/>
+      <c r="DX1" s="81"/>
+      <c r="DY1" s="81"/>
+      <c r="DZ1" s="81"/>
+      <c r="EA1" s="81"/>
+      <c r="EB1" s="81"/>
+      <c r="EC1" s="81"/>
+      <c r="ED1" s="81"/>
+      <c r="EE1" s="81"/>
+      <c r="EF1" s="81"/>
+      <c r="EG1" s="81"/>
+      <c r="EH1" s="81"/>
+      <c r="EI1" s="81"/>
+      <c r="EJ1" s="81"/>
+      <c r="EK1" s="81"/>
+      <c r="EL1" s="81"/>
+      <c r="EM1" s="81"/>
+      <c r="EN1" s="81"/>
+      <c r="EO1" s="81"/>
+      <c r="EP1" s="81"/>
+      <c r="EQ1" s="81"/>
+      <c r="ER1" s="81"/>
+      <c r="ES1" s="81"/>
+      <c r="ET1" s="81"/>
+      <c r="EU1" s="81"/>
+      <c r="EV1" s="81"/>
+      <c r="EW1" s="81"/>
+      <c r="EX1" s="81"/>
+      <c r="EY1" s="81"/>
+      <c r="EZ1" s="81"/>
+      <c r="FA1" s="81"/>
+      <c r="FB1" s="81"/>
+      <c r="FC1" s="81"/>
+      <c r="FD1" s="81"/>
+      <c r="FE1" s="81"/>
+      <c r="FF1" s="81"/>
+      <c r="FG1" s="81"/>
+      <c r="FH1" s="81"/>
+      <c r="FI1" s="81"/>
+      <c r="FJ1" s="81"/>
+      <c r="FK1" s="81"/>
+      <c r="FL1" s="81"/>
+      <c r="FM1" s="81"/>
+      <c r="FN1" s="81"/>
+      <c r="FO1" s="81"/>
+      <c r="FP1" s="81"/>
+      <c r="FQ1" s="81"/>
+      <c r="FR1" s="81"/>
+      <c r="FS1" s="81"/>
+      <c r="FT1" s="81"/>
+      <c r="FU1" s="81"/>
+      <c r="FV1" s="81"/>
+      <c r="FW1" s="81"/>
+      <c r="FX1" s="81"/>
+      <c r="FY1" s="81"/>
+      <c r="FZ1" s="81"/>
+      <c r="GA1" s="81"/>
+      <c r="GB1" s="81"/>
+      <c r="GC1" s="81"/>
+      <c r="GD1" s="81"/>
+      <c r="GE1" s="81"/>
+      <c r="GF1" s="81"/>
+      <c r="GG1" s="81"/>
+      <c r="GH1" s="81"/>
+      <c r="GI1" s="81"/>
+      <c r="GJ1" s="81"/>
+      <c r="GK1" s="81"/>
+      <c r="GL1" s="81"/>
+      <c r="GM1" s="81"/>
+      <c r="GN1" s="81"/>
+      <c r="GO1" s="81"/>
+      <c r="GP1" s="81"/>
+      <c r="GQ1" s="81"/>
+      <c r="GR1" s="81"/>
+      <c r="GS1" s="81"/>
+      <c r="GT1" s="81"/>
+      <c r="GU1" s="81"/>
+      <c r="GV1" s="81"/>
+      <c r="GW1" s="81"/>
+      <c r="GX1" s="81"/>
+      <c r="GY1" s="81"/>
+      <c r="GZ1" s="81"/>
+      <c r="HA1" s="81"/>
+      <c r="HB1" s="81"/>
+      <c r="HC1" s="81"/>
+      <c r="HD1" s="81"/>
+      <c r="HE1" s="81"/>
+      <c r="HF1" s="81"/>
+      <c r="HG1" s="81"/>
+      <c r="HH1" s="81"/>
+      <c r="HI1" s="81"/>
     </row>
     <row r="2" spans="1:217" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="122">
+      <c r="B2" s="80">
         <v>0</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="122">
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="80">
         <v>1</v>
       </c>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="122">
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="80">
         <v>2</v>
       </c>
-      <c r="S2" s="123"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="123"/>
-      <c r="V2" s="123"/>
-      <c r="W2" s="123"/>
-      <c r="X2" s="123"/>
-      <c r="Y2" s="124"/>
-      <c r="Z2" s="122">
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="82"/>
+      <c r="Z2" s="80">
         <v>3</v>
       </c>
-      <c r="AA2" s="123"/>
-      <c r="AB2" s="123"/>
-      <c r="AC2" s="123"/>
-      <c r="AD2" s="123"/>
-      <c r="AE2" s="123"/>
-      <c r="AF2" s="123"/>
-      <c r="AG2" s="124"/>
-      <c r="AH2" s="122">
+      <c r="AA2" s="81"/>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="81"/>
+      <c r="AE2" s="81"/>
+      <c r="AF2" s="81"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="80">
         <v>4</v>
       </c>
-      <c r="AI2" s="123"/>
-      <c r="AJ2" s="123"/>
-      <c r="AK2" s="123"/>
-      <c r="AL2" s="123"/>
-      <c r="AM2" s="123"/>
-      <c r="AN2" s="123"/>
-      <c r="AO2" s="124"/>
-      <c r="AP2" s="122">
+      <c r="AI2" s="81"/>
+      <c r="AJ2" s="81"/>
+      <c r="AK2" s="81"/>
+      <c r="AL2" s="81"/>
+      <c r="AM2" s="81"/>
+      <c r="AN2" s="81"/>
+      <c r="AO2" s="82"/>
+      <c r="AP2" s="80">
         <v>5</v>
       </c>
-      <c r="AQ2" s="123"/>
-      <c r="AR2" s="123"/>
-      <c r="AS2" s="123"/>
-      <c r="AT2" s="123"/>
-      <c r="AU2" s="123"/>
-      <c r="AV2" s="123"/>
-      <c r="AW2" s="124"/>
-      <c r="AX2" s="122">
+      <c r="AQ2" s="81"/>
+      <c r="AR2" s="81"/>
+      <c r="AS2" s="81"/>
+      <c r="AT2" s="81"/>
+      <c r="AU2" s="81"/>
+      <c r="AV2" s="81"/>
+      <c r="AW2" s="82"/>
+      <c r="AX2" s="80">
         <v>6</v>
       </c>
-      <c r="AY2" s="123"/>
-      <c r="AZ2" s="123"/>
-      <c r="BA2" s="123"/>
-      <c r="BB2" s="123"/>
-      <c r="BC2" s="123"/>
-      <c r="BD2" s="123"/>
-      <c r="BE2" s="124"/>
-      <c r="BF2" s="122">
+      <c r="AY2" s="81"/>
+      <c r="AZ2" s="81"/>
+      <c r="BA2" s="81"/>
+      <c r="BB2" s="81"/>
+      <c r="BC2" s="81"/>
+      <c r="BD2" s="81"/>
+      <c r="BE2" s="82"/>
+      <c r="BF2" s="80">
         <v>7</v>
       </c>
-      <c r="BG2" s="123"/>
-      <c r="BH2" s="123"/>
-      <c r="BI2" s="123"/>
-      <c r="BJ2" s="123"/>
-      <c r="BK2" s="123"/>
-      <c r="BL2" s="123"/>
-      <c r="BM2" s="124"/>
-      <c r="BN2" s="122">
+      <c r="BG2" s="81"/>
+      <c r="BH2" s="81"/>
+      <c r="BI2" s="81"/>
+      <c r="BJ2" s="81"/>
+      <c r="BK2" s="81"/>
+      <c r="BL2" s="81"/>
+      <c r="BM2" s="82"/>
+      <c r="BN2" s="80">
         <v>8</v>
       </c>
-      <c r="BO2" s="123"/>
-      <c r="BP2" s="123"/>
-      <c r="BQ2" s="123"/>
-      <c r="BR2" s="123"/>
-      <c r="BS2" s="123"/>
-      <c r="BT2" s="123"/>
-      <c r="BU2" s="124"/>
-      <c r="BV2" s="122">
+      <c r="BO2" s="81"/>
+      <c r="BP2" s="81"/>
+      <c r="BQ2" s="81"/>
+      <c r="BR2" s="81"/>
+      <c r="BS2" s="81"/>
+      <c r="BT2" s="81"/>
+      <c r="BU2" s="82"/>
+      <c r="BV2" s="80">
         <v>9</v>
       </c>
-      <c r="BW2" s="123"/>
-      <c r="BX2" s="123"/>
-      <c r="BY2" s="123"/>
-      <c r="BZ2" s="123"/>
-      <c r="CA2" s="123"/>
-      <c r="CB2" s="123"/>
-      <c r="CC2" s="124"/>
-      <c r="CD2" s="122">
+      <c r="BW2" s="81"/>
+      <c r="BX2" s="81"/>
+      <c r="BY2" s="81"/>
+      <c r="BZ2" s="81"/>
+      <c r="CA2" s="81"/>
+      <c r="CB2" s="81"/>
+      <c r="CC2" s="82"/>
+      <c r="CD2" s="80">
         <v>10</v>
       </c>
-      <c r="CE2" s="123"/>
-      <c r="CF2" s="123"/>
-      <c r="CG2" s="123"/>
-      <c r="CH2" s="123"/>
-      <c r="CI2" s="123"/>
-      <c r="CJ2" s="123"/>
-      <c r="CK2" s="124"/>
-      <c r="CL2" s="122">
+      <c r="CE2" s="81"/>
+      <c r="CF2" s="81"/>
+      <c r="CG2" s="81"/>
+      <c r="CH2" s="81"/>
+      <c r="CI2" s="81"/>
+      <c r="CJ2" s="81"/>
+      <c r="CK2" s="82"/>
+      <c r="CL2" s="80">
         <v>11</v>
       </c>
-      <c r="CM2" s="123"/>
-      <c r="CN2" s="123"/>
-      <c r="CO2" s="123"/>
-      <c r="CP2" s="123"/>
-      <c r="CQ2" s="123"/>
-      <c r="CR2" s="123"/>
-      <c r="CS2" s="124"/>
-      <c r="CT2" s="122">
+      <c r="CM2" s="81"/>
+      <c r="CN2" s="81"/>
+      <c r="CO2" s="81"/>
+      <c r="CP2" s="81"/>
+      <c r="CQ2" s="81"/>
+      <c r="CR2" s="81"/>
+      <c r="CS2" s="82"/>
+      <c r="CT2" s="80">
         <v>12</v>
       </c>
-      <c r="CU2" s="123"/>
-      <c r="CV2" s="123"/>
-      <c r="CW2" s="123"/>
-      <c r="CX2" s="123"/>
-      <c r="CY2" s="123"/>
-      <c r="CZ2" s="123"/>
-      <c r="DA2" s="124"/>
-      <c r="DB2" s="122">
+      <c r="CU2" s="81"/>
+      <c r="CV2" s="81"/>
+      <c r="CW2" s="81"/>
+      <c r="CX2" s="81"/>
+      <c r="CY2" s="81"/>
+      <c r="CZ2" s="81"/>
+      <c r="DA2" s="82"/>
+      <c r="DB2" s="80">
         <v>13</v>
       </c>
-      <c r="DC2" s="123"/>
-      <c r="DD2" s="123"/>
-      <c r="DE2" s="123"/>
-      <c r="DF2" s="123"/>
-      <c r="DG2" s="123"/>
-      <c r="DH2" s="123"/>
-      <c r="DI2" s="124"/>
-      <c r="DJ2" s="122">
+      <c r="DC2" s="81"/>
+      <c r="DD2" s="81"/>
+      <c r="DE2" s="81"/>
+      <c r="DF2" s="81"/>
+      <c r="DG2" s="81"/>
+      <c r="DH2" s="81"/>
+      <c r="DI2" s="82"/>
+      <c r="DJ2" s="80">
         <v>14</v>
       </c>
-      <c r="DK2" s="123"/>
-      <c r="DL2" s="123"/>
-      <c r="DM2" s="123"/>
-      <c r="DN2" s="123"/>
-      <c r="DO2" s="123"/>
-      <c r="DP2" s="123"/>
-      <c r="DQ2" s="124"/>
-      <c r="DR2" s="122">
+      <c r="DK2" s="81"/>
+      <c r="DL2" s="81"/>
+      <c r="DM2" s="81"/>
+      <c r="DN2" s="81"/>
+      <c r="DO2" s="81"/>
+      <c r="DP2" s="81"/>
+      <c r="DQ2" s="82"/>
+      <c r="DR2" s="80">
         <v>15</v>
       </c>
-      <c r="DS2" s="123"/>
-      <c r="DT2" s="123"/>
-      <c r="DU2" s="123"/>
-      <c r="DV2" s="123"/>
-      <c r="DW2" s="123"/>
-      <c r="DX2" s="123"/>
-      <c r="DY2" s="124"/>
-      <c r="DZ2" s="122">
+      <c r="DS2" s="81"/>
+      <c r="DT2" s="81"/>
+      <c r="DU2" s="81"/>
+      <c r="DV2" s="81"/>
+      <c r="DW2" s="81"/>
+      <c r="DX2" s="81"/>
+      <c r="DY2" s="82"/>
+      <c r="DZ2" s="80">
         <v>16</v>
       </c>
-      <c r="EA2" s="123"/>
-      <c r="EB2" s="123"/>
-      <c r="EC2" s="123"/>
-      <c r="ED2" s="123"/>
-      <c r="EE2" s="123"/>
-      <c r="EF2" s="123"/>
-      <c r="EG2" s="124"/>
-      <c r="EH2" s="122">
+      <c r="EA2" s="81"/>
+      <c r="EB2" s="81"/>
+      <c r="EC2" s="81"/>
+      <c r="ED2" s="81"/>
+      <c r="EE2" s="81"/>
+      <c r="EF2" s="81"/>
+      <c r="EG2" s="82"/>
+      <c r="EH2" s="80">
         <v>17</v>
       </c>
-      <c r="EI2" s="123"/>
-      <c r="EJ2" s="123"/>
-      <c r="EK2" s="123"/>
-      <c r="EL2" s="123"/>
-      <c r="EM2" s="123"/>
-      <c r="EN2" s="123"/>
-      <c r="EO2" s="124"/>
-      <c r="EP2" s="122">
+      <c r="EI2" s="81"/>
+      <c r="EJ2" s="81"/>
+      <c r="EK2" s="81"/>
+      <c r="EL2" s="81"/>
+      <c r="EM2" s="81"/>
+      <c r="EN2" s="81"/>
+      <c r="EO2" s="82"/>
+      <c r="EP2" s="80">
         <v>18</v>
       </c>
-      <c r="EQ2" s="123"/>
-      <c r="ER2" s="123"/>
-      <c r="ES2" s="123"/>
-      <c r="ET2" s="123"/>
-      <c r="EU2" s="123"/>
-      <c r="EV2" s="123"/>
-      <c r="EW2" s="124"/>
-      <c r="EX2" s="122">
+      <c r="EQ2" s="81"/>
+      <c r="ER2" s="81"/>
+      <c r="ES2" s="81"/>
+      <c r="ET2" s="81"/>
+      <c r="EU2" s="81"/>
+      <c r="EV2" s="81"/>
+      <c r="EW2" s="82"/>
+      <c r="EX2" s="80">
         <v>19</v>
       </c>
-      <c r="EY2" s="123"/>
-      <c r="EZ2" s="123"/>
-      <c r="FA2" s="123"/>
-      <c r="FB2" s="123"/>
-      <c r="FC2" s="123"/>
-      <c r="FD2" s="123"/>
-      <c r="FE2" s="124"/>
-      <c r="FF2" s="122">
+      <c r="EY2" s="81"/>
+      <c r="EZ2" s="81"/>
+      <c r="FA2" s="81"/>
+      <c r="FB2" s="81"/>
+      <c r="FC2" s="81"/>
+      <c r="FD2" s="81"/>
+      <c r="FE2" s="82"/>
+      <c r="FF2" s="80">
         <v>20</v>
       </c>
-      <c r="FG2" s="123"/>
-      <c r="FH2" s="123"/>
-      <c r="FI2" s="123"/>
-      <c r="FJ2" s="123"/>
-      <c r="FK2" s="123"/>
-      <c r="FL2" s="123"/>
-      <c r="FM2" s="124"/>
-      <c r="FN2" s="122">
+      <c r="FG2" s="81"/>
+      <c r="FH2" s="81"/>
+      <c r="FI2" s="81"/>
+      <c r="FJ2" s="81"/>
+      <c r="FK2" s="81"/>
+      <c r="FL2" s="81"/>
+      <c r="FM2" s="82"/>
+      <c r="FN2" s="80">
         <v>21</v>
       </c>
-      <c r="FO2" s="123"/>
-      <c r="FP2" s="123"/>
-      <c r="FQ2" s="123"/>
-      <c r="FR2" s="123"/>
-      <c r="FS2" s="123"/>
-      <c r="FT2" s="123"/>
-      <c r="FU2" s="124"/>
-      <c r="FV2" s="122">
+      <c r="FO2" s="81"/>
+      <c r="FP2" s="81"/>
+      <c r="FQ2" s="81"/>
+      <c r="FR2" s="81"/>
+      <c r="FS2" s="81"/>
+      <c r="FT2" s="81"/>
+      <c r="FU2" s="82"/>
+      <c r="FV2" s="80">
         <v>22</v>
       </c>
-      <c r="FW2" s="123"/>
-      <c r="FX2" s="123"/>
-      <c r="FY2" s="123"/>
-      <c r="FZ2" s="123"/>
-      <c r="GA2" s="123"/>
-      <c r="GB2" s="123"/>
-      <c r="GC2" s="124"/>
-      <c r="GD2" s="122">
+      <c r="FW2" s="81"/>
+      <c r="FX2" s="81"/>
+      <c r="FY2" s="81"/>
+      <c r="FZ2" s="81"/>
+      <c r="GA2" s="81"/>
+      <c r="GB2" s="81"/>
+      <c r="GC2" s="82"/>
+      <c r="GD2" s="80">
         <v>23</v>
       </c>
-      <c r="GE2" s="123"/>
-      <c r="GF2" s="123"/>
-      <c r="GG2" s="123"/>
-      <c r="GH2" s="123"/>
-      <c r="GI2" s="123"/>
-      <c r="GJ2" s="123"/>
-      <c r="GK2" s="124"/>
-      <c r="GL2" s="122">
+      <c r="GE2" s="81"/>
+      <c r="GF2" s="81"/>
+      <c r="GG2" s="81"/>
+      <c r="GH2" s="81"/>
+      <c r="GI2" s="81"/>
+      <c r="GJ2" s="81"/>
+      <c r="GK2" s="82"/>
+      <c r="GL2" s="80">
         <v>24</v>
       </c>
-      <c r="GM2" s="123"/>
-      <c r="GN2" s="123"/>
-      <c r="GO2" s="123"/>
-      <c r="GP2" s="123"/>
-      <c r="GQ2" s="123"/>
-      <c r="GR2" s="123"/>
-      <c r="GS2" s="124"/>
-      <c r="GT2" s="122">
+      <c r="GM2" s="81"/>
+      <c r="GN2" s="81"/>
+      <c r="GO2" s="81"/>
+      <c r="GP2" s="81"/>
+      <c r="GQ2" s="81"/>
+      <c r="GR2" s="81"/>
+      <c r="GS2" s="82"/>
+      <c r="GT2" s="80">
         <v>25</v>
       </c>
-      <c r="GU2" s="123"/>
-      <c r="GV2" s="123"/>
-      <c r="GW2" s="123"/>
-      <c r="GX2" s="123"/>
-      <c r="GY2" s="123"/>
-      <c r="GZ2" s="123"/>
-      <c r="HA2" s="124"/>
-      <c r="HB2" s="122">
+      <c r="GU2" s="81"/>
+      <c r="GV2" s="81"/>
+      <c r="GW2" s="81"/>
+      <c r="GX2" s="81"/>
+      <c r="GY2" s="81"/>
+      <c r="GZ2" s="81"/>
+      <c r="HA2" s="82"/>
+      <c r="HB2" s="80">
         <v>26</v>
       </c>
-      <c r="HC2" s="123"/>
-      <c r="HD2" s="123"/>
-      <c r="HE2" s="123"/>
-      <c r="HF2" s="123"/>
-      <c r="HG2" s="123"/>
-      <c r="HH2" s="123"/>
-      <c r="HI2" s="124"/>
+      <c r="HC2" s="81"/>
+      <c r="HD2" s="81"/>
+      <c r="HE2" s="81"/>
+      <c r="HF2" s="81"/>
+      <c r="HG2" s="81"/>
+      <c r="HH2" s="81"/>
+      <c r="HI2" s="82"/>
     </row>
     <row r="3" spans="1:217" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="122" t="str">
+      <c r="B3" s="80" t="str">
         <f>DEC2HEX(B2)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="122" t="str">
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="80" t="str">
         <f t="shared" ref="J3" si="0">DEC2HEX(J2)</f>
         <v>1</v>
       </c>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="123"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="123"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="122" t="str">
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="80" t="str">
         <f t="shared" ref="R3" si="1">DEC2HEX(R2)</f>
         <v>2</v>
       </c>
-      <c r="S3" s="123"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="124"/>
-      <c r="Z3" s="122" t="str">
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="80" t="str">
         <f t="shared" ref="Z3" si="2">DEC2HEX(Z2)</f>
         <v>3</v>
       </c>
-      <c r="AA3" s="123"/>
-      <c r="AB3" s="123"/>
-      <c r="AC3" s="123"/>
-      <c r="AD3" s="123"/>
-      <c r="AE3" s="123"/>
-      <c r="AF3" s="123"/>
-      <c r="AG3" s="124"/>
-      <c r="AH3" s="122" t="str">
+      <c r="AA3" s="81"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="81"/>
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="81"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="80" t="str">
         <f t="shared" ref="AH3" si="3">DEC2HEX(AH2)</f>
         <v>4</v>
       </c>
-      <c r="AI3" s="123"/>
-      <c r="AJ3" s="123"/>
-      <c r="AK3" s="123"/>
-      <c r="AL3" s="123"/>
-      <c r="AM3" s="123"/>
-      <c r="AN3" s="123"/>
-      <c r="AO3" s="124"/>
-      <c r="AP3" s="122" t="str">
+      <c r="AI3" s="81"/>
+      <c r="AJ3" s="81"/>
+      <c r="AK3" s="81"/>
+      <c r="AL3" s="81"/>
+      <c r="AM3" s="81"/>
+      <c r="AN3" s="81"/>
+      <c r="AO3" s="82"/>
+      <c r="AP3" s="80" t="str">
         <f t="shared" ref="AP3" si="4">DEC2HEX(AP2)</f>
         <v>5</v>
       </c>
-      <c r="AQ3" s="123"/>
-      <c r="AR3" s="123"/>
-      <c r="AS3" s="123"/>
-      <c r="AT3" s="123"/>
-      <c r="AU3" s="123"/>
-      <c r="AV3" s="123"/>
-      <c r="AW3" s="124"/>
-      <c r="AX3" s="122" t="str">
+      <c r="AQ3" s="81"/>
+      <c r="AR3" s="81"/>
+      <c r="AS3" s="81"/>
+      <c r="AT3" s="81"/>
+      <c r="AU3" s="81"/>
+      <c r="AV3" s="81"/>
+      <c r="AW3" s="82"/>
+      <c r="AX3" s="80" t="str">
         <f t="shared" ref="AX3" si="5">DEC2HEX(AX2)</f>
         <v>6</v>
       </c>
-      <c r="AY3" s="123"/>
-      <c r="AZ3" s="123"/>
-      <c r="BA3" s="123"/>
-      <c r="BB3" s="123"/>
-      <c r="BC3" s="123"/>
-      <c r="BD3" s="123"/>
-      <c r="BE3" s="124"/>
-      <c r="BF3" s="122" t="str">
+      <c r="AY3" s="81"/>
+      <c r="AZ3" s="81"/>
+      <c r="BA3" s="81"/>
+      <c r="BB3" s="81"/>
+      <c r="BC3" s="81"/>
+      <c r="BD3" s="81"/>
+      <c r="BE3" s="82"/>
+      <c r="BF3" s="80" t="str">
         <f t="shared" ref="BF3" si="6">DEC2HEX(BF2)</f>
         <v>7</v>
       </c>
-      <c r="BG3" s="123"/>
-      <c r="BH3" s="123"/>
-      <c r="BI3" s="123"/>
-      <c r="BJ3" s="123"/>
-      <c r="BK3" s="123"/>
-      <c r="BL3" s="123"/>
-      <c r="BM3" s="124"/>
-      <c r="BN3" s="122" t="str">
+      <c r="BG3" s="81"/>
+      <c r="BH3" s="81"/>
+      <c r="BI3" s="81"/>
+      <c r="BJ3" s="81"/>
+      <c r="BK3" s="81"/>
+      <c r="BL3" s="81"/>
+      <c r="BM3" s="82"/>
+      <c r="BN3" s="80" t="str">
         <f t="shared" ref="BN3" si="7">DEC2HEX(BN2)</f>
         <v>8</v>
       </c>
-      <c r="BO3" s="123"/>
-      <c r="BP3" s="123"/>
-      <c r="BQ3" s="123"/>
-      <c r="BR3" s="123"/>
-      <c r="BS3" s="123"/>
-      <c r="BT3" s="123"/>
-      <c r="BU3" s="124"/>
-      <c r="BV3" s="122" t="str">
+      <c r="BO3" s="81"/>
+      <c r="BP3" s="81"/>
+      <c r="BQ3" s="81"/>
+      <c r="BR3" s="81"/>
+      <c r="BS3" s="81"/>
+      <c r="BT3" s="81"/>
+      <c r="BU3" s="82"/>
+      <c r="BV3" s="80" t="str">
         <f t="shared" ref="BV3" si="8">DEC2HEX(BV2)</f>
         <v>9</v>
       </c>
-      <c r="BW3" s="123"/>
-      <c r="BX3" s="123"/>
-      <c r="BY3" s="123"/>
-      <c r="BZ3" s="123"/>
-      <c r="CA3" s="123"/>
-      <c r="CB3" s="123"/>
-      <c r="CC3" s="124"/>
-      <c r="CD3" s="122" t="str">
+      <c r="BW3" s="81"/>
+      <c r="BX3" s="81"/>
+      <c r="BY3" s="81"/>
+      <c r="BZ3" s="81"/>
+      <c r="CA3" s="81"/>
+      <c r="CB3" s="81"/>
+      <c r="CC3" s="82"/>
+      <c r="CD3" s="80" t="str">
         <f t="shared" ref="CD3" si="9">DEC2HEX(CD2)</f>
         <v>A</v>
       </c>
-      <c r="CE3" s="123"/>
-      <c r="CF3" s="123"/>
-      <c r="CG3" s="123"/>
-      <c r="CH3" s="123"/>
-      <c r="CI3" s="123"/>
-      <c r="CJ3" s="123"/>
-      <c r="CK3" s="124"/>
-      <c r="CL3" s="122" t="str">
+      <c r="CE3" s="81"/>
+      <c r="CF3" s="81"/>
+      <c r="CG3" s="81"/>
+      <c r="CH3" s="81"/>
+      <c r="CI3" s="81"/>
+      <c r="CJ3" s="81"/>
+      <c r="CK3" s="82"/>
+      <c r="CL3" s="80" t="str">
         <f t="shared" ref="CL3" si="10">DEC2HEX(CL2)</f>
         <v>B</v>
       </c>
-      <c r="CM3" s="123"/>
-      <c r="CN3" s="123"/>
-      <c r="CO3" s="123"/>
-      <c r="CP3" s="123"/>
-      <c r="CQ3" s="123"/>
-      <c r="CR3" s="123"/>
-      <c r="CS3" s="124"/>
-      <c r="CT3" s="122" t="str">
+      <c r="CM3" s="81"/>
+      <c r="CN3" s="81"/>
+      <c r="CO3" s="81"/>
+      <c r="CP3" s="81"/>
+      <c r="CQ3" s="81"/>
+      <c r="CR3" s="81"/>
+      <c r="CS3" s="82"/>
+      <c r="CT3" s="80" t="str">
         <f t="shared" ref="CT3" si="11">DEC2HEX(CT2)</f>
         <v>C</v>
       </c>
-      <c r="CU3" s="123"/>
-      <c r="CV3" s="123"/>
-      <c r="CW3" s="123"/>
-      <c r="CX3" s="123"/>
-      <c r="CY3" s="123"/>
-      <c r="CZ3" s="123"/>
-      <c r="DA3" s="124"/>
-      <c r="DB3" s="122" t="str">
+      <c r="CU3" s="81"/>
+      <c r="CV3" s="81"/>
+      <c r="CW3" s="81"/>
+      <c r="CX3" s="81"/>
+      <c r="CY3" s="81"/>
+      <c r="CZ3" s="81"/>
+      <c r="DA3" s="82"/>
+      <c r="DB3" s="80" t="str">
         <f t="shared" ref="DB3" si="12">DEC2HEX(DB2)</f>
         <v>D</v>
       </c>
-      <c r="DC3" s="123"/>
-      <c r="DD3" s="123"/>
-      <c r="DE3" s="123"/>
-      <c r="DF3" s="123"/>
-      <c r="DG3" s="123"/>
-      <c r="DH3" s="123"/>
-      <c r="DI3" s="124"/>
-      <c r="DJ3" s="122" t="str">
+      <c r="DC3" s="81"/>
+      <c r="DD3" s="81"/>
+      <c r="DE3" s="81"/>
+      <c r="DF3" s="81"/>
+      <c r="DG3" s="81"/>
+      <c r="DH3" s="81"/>
+      <c r="DI3" s="82"/>
+      <c r="DJ3" s="80" t="str">
         <f t="shared" ref="DJ3" si="13">DEC2HEX(DJ2)</f>
         <v>E</v>
       </c>
-      <c r="DK3" s="123"/>
-      <c r="DL3" s="123"/>
-      <c r="DM3" s="123"/>
-      <c r="DN3" s="123"/>
-      <c r="DO3" s="123"/>
-      <c r="DP3" s="123"/>
-      <c r="DQ3" s="124"/>
-      <c r="DR3" s="122" t="str">
+      <c r="DK3" s="81"/>
+      <c r="DL3" s="81"/>
+      <c r="DM3" s="81"/>
+      <c r="DN3" s="81"/>
+      <c r="DO3" s="81"/>
+      <c r="DP3" s="81"/>
+      <c r="DQ3" s="82"/>
+      <c r="DR3" s="80" t="str">
         <f t="shared" ref="DR3" si="14">DEC2HEX(DR2)</f>
         <v>F</v>
       </c>
-      <c r="DS3" s="123"/>
-      <c r="DT3" s="123"/>
-      <c r="DU3" s="123"/>
-      <c r="DV3" s="123"/>
-      <c r="DW3" s="123"/>
-      <c r="DX3" s="123"/>
-      <c r="DY3" s="124"/>
-      <c r="DZ3" s="122" t="str">
+      <c r="DS3" s="81"/>
+      <c r="DT3" s="81"/>
+      <c r="DU3" s="81"/>
+      <c r="DV3" s="81"/>
+      <c r="DW3" s="81"/>
+      <c r="DX3" s="81"/>
+      <c r="DY3" s="82"/>
+      <c r="DZ3" s="80" t="str">
         <f t="shared" ref="DZ3" si="15">DEC2HEX(DZ2)</f>
         <v>10</v>
       </c>
-      <c r="EA3" s="123"/>
-      <c r="EB3" s="123"/>
-      <c r="EC3" s="123"/>
-      <c r="ED3" s="123"/>
-      <c r="EE3" s="123"/>
-      <c r="EF3" s="123"/>
-      <c r="EG3" s="124"/>
-      <c r="EH3" s="122" t="str">
+      <c r="EA3" s="81"/>
+      <c r="EB3" s="81"/>
+      <c r="EC3" s="81"/>
+      <c r="ED3" s="81"/>
+      <c r="EE3" s="81"/>
+      <c r="EF3" s="81"/>
+      <c r="EG3" s="82"/>
+      <c r="EH3" s="80" t="str">
         <f t="shared" ref="EH3" si="16">DEC2HEX(EH2)</f>
         <v>11</v>
       </c>
-      <c r="EI3" s="123"/>
-      <c r="EJ3" s="123"/>
-      <c r="EK3" s="123"/>
-      <c r="EL3" s="123"/>
-      <c r="EM3" s="123"/>
-      <c r="EN3" s="123"/>
-      <c r="EO3" s="124"/>
-      <c r="EP3" s="122" t="str">
+      <c r="EI3" s="81"/>
+      <c r="EJ3" s="81"/>
+      <c r="EK3" s="81"/>
+      <c r="EL3" s="81"/>
+      <c r="EM3" s="81"/>
+      <c r="EN3" s="81"/>
+      <c r="EO3" s="82"/>
+      <c r="EP3" s="80" t="str">
         <f t="shared" ref="EP3" si="17">DEC2HEX(EP2)</f>
         <v>12</v>
       </c>
-      <c r="EQ3" s="123"/>
-      <c r="ER3" s="123"/>
-      <c r="ES3" s="123"/>
-      <c r="ET3" s="123"/>
-      <c r="EU3" s="123"/>
-      <c r="EV3" s="123"/>
-      <c r="EW3" s="124"/>
-      <c r="EX3" s="122" t="str">
+      <c r="EQ3" s="81"/>
+      <c r="ER3" s="81"/>
+      <c r="ES3" s="81"/>
+      <c r="ET3" s="81"/>
+      <c r="EU3" s="81"/>
+      <c r="EV3" s="81"/>
+      <c r="EW3" s="82"/>
+      <c r="EX3" s="80" t="str">
         <f t="shared" ref="EX3" si="18">DEC2HEX(EX2)</f>
         <v>13</v>
       </c>
-      <c r="EY3" s="123"/>
-      <c r="EZ3" s="123"/>
-      <c r="FA3" s="123"/>
-      <c r="FB3" s="123"/>
-      <c r="FC3" s="123"/>
-      <c r="FD3" s="123"/>
-      <c r="FE3" s="124"/>
-      <c r="FF3" s="122" t="str">
+      <c r="EY3" s="81"/>
+      <c r="EZ3" s="81"/>
+      <c r="FA3" s="81"/>
+      <c r="FB3" s="81"/>
+      <c r="FC3" s="81"/>
+      <c r="FD3" s="81"/>
+      <c r="FE3" s="82"/>
+      <c r="FF3" s="80" t="str">
         <f t="shared" ref="FF3" si="19">DEC2HEX(FF2)</f>
         <v>14</v>
       </c>
-      <c r="FG3" s="123"/>
-      <c r="FH3" s="123"/>
-      <c r="FI3" s="123"/>
-      <c r="FJ3" s="123"/>
-      <c r="FK3" s="123"/>
-      <c r="FL3" s="123"/>
-      <c r="FM3" s="124"/>
-      <c r="FN3" s="122" t="str">
+      <c r="FG3" s="81"/>
+      <c r="FH3" s="81"/>
+      <c r="FI3" s="81"/>
+      <c r="FJ3" s="81"/>
+      <c r="FK3" s="81"/>
+      <c r="FL3" s="81"/>
+      <c r="FM3" s="82"/>
+      <c r="FN3" s="80" t="str">
         <f t="shared" ref="FN3" si="20">DEC2HEX(FN2)</f>
         <v>15</v>
       </c>
-      <c r="FO3" s="123"/>
-      <c r="FP3" s="123"/>
-      <c r="FQ3" s="123"/>
-      <c r="FR3" s="123"/>
-      <c r="FS3" s="123"/>
-      <c r="FT3" s="123"/>
-      <c r="FU3" s="124"/>
-      <c r="FV3" s="122" t="str">
+      <c r="FO3" s="81"/>
+      <c r="FP3" s="81"/>
+      <c r="FQ3" s="81"/>
+      <c r="FR3" s="81"/>
+      <c r="FS3" s="81"/>
+      <c r="FT3" s="81"/>
+      <c r="FU3" s="82"/>
+      <c r="FV3" s="80" t="str">
         <f t="shared" ref="FV3" si="21">DEC2HEX(FV2)</f>
         <v>16</v>
       </c>
-      <c r="FW3" s="123"/>
-      <c r="FX3" s="123"/>
-      <c r="FY3" s="123"/>
-      <c r="FZ3" s="123"/>
-      <c r="GA3" s="123"/>
-      <c r="GB3" s="123"/>
-      <c r="GC3" s="124"/>
-      <c r="GD3" s="122" t="str">
+      <c r="FW3" s="81"/>
+      <c r="FX3" s="81"/>
+      <c r="FY3" s="81"/>
+      <c r="FZ3" s="81"/>
+      <c r="GA3" s="81"/>
+      <c r="GB3" s="81"/>
+      <c r="GC3" s="82"/>
+      <c r="GD3" s="80" t="str">
         <f t="shared" ref="GD3" si="22">DEC2HEX(GD2)</f>
         <v>17</v>
       </c>
-      <c r="GE3" s="123"/>
-      <c r="GF3" s="123"/>
-      <c r="GG3" s="123"/>
-      <c r="GH3" s="123"/>
-      <c r="GI3" s="123"/>
-      <c r="GJ3" s="123"/>
-      <c r="GK3" s="124"/>
-      <c r="GL3" s="122" t="str">
+      <c r="GE3" s="81"/>
+      <c r="GF3" s="81"/>
+      <c r="GG3" s="81"/>
+      <c r="GH3" s="81"/>
+      <c r="GI3" s="81"/>
+      <c r="GJ3" s="81"/>
+      <c r="GK3" s="82"/>
+      <c r="GL3" s="80" t="str">
         <f t="shared" ref="GL3" si="23">DEC2HEX(GL2)</f>
         <v>18</v>
       </c>
-      <c r="GM3" s="123"/>
-      <c r="GN3" s="123"/>
-      <c r="GO3" s="123"/>
-      <c r="GP3" s="123"/>
-      <c r="GQ3" s="123"/>
-      <c r="GR3" s="123"/>
-      <c r="GS3" s="124"/>
-      <c r="GT3" s="122" t="str">
+      <c r="GM3" s="81"/>
+      <c r="GN3" s="81"/>
+      <c r="GO3" s="81"/>
+      <c r="GP3" s="81"/>
+      <c r="GQ3" s="81"/>
+      <c r="GR3" s="81"/>
+      <c r="GS3" s="82"/>
+      <c r="GT3" s="80" t="str">
         <f t="shared" ref="GT3" si="24">DEC2HEX(GT2)</f>
         <v>19</v>
       </c>
-      <c r="GU3" s="123"/>
-      <c r="GV3" s="123"/>
-      <c r="GW3" s="123"/>
-      <c r="GX3" s="123"/>
-      <c r="GY3" s="123"/>
-      <c r="GZ3" s="123"/>
-      <c r="HA3" s="124"/>
-      <c r="HB3" s="122" t="str">
+      <c r="GU3" s="81"/>
+      <c r="GV3" s="81"/>
+      <c r="GW3" s="81"/>
+      <c r="GX3" s="81"/>
+      <c r="GY3" s="81"/>
+      <c r="GZ3" s="81"/>
+      <c r="HA3" s="82"/>
+      <c r="HB3" s="80" t="str">
         <f t="shared" ref="HB3" si="25">DEC2HEX(HB2)</f>
         <v>1A</v>
       </c>
-      <c r="HC3" s="123"/>
-      <c r="HD3" s="123"/>
-      <c r="HE3" s="123"/>
-      <c r="HF3" s="123"/>
-      <c r="HG3" s="123"/>
-      <c r="HH3" s="123"/>
-      <c r="HI3" s="124"/>
+      <c r="HC3" s="81"/>
+      <c r="HD3" s="81"/>
+      <c r="HE3" s="81"/>
+      <c r="HF3" s="81"/>
+      <c r="HG3" s="81"/>
+      <c r="HH3" s="81"/>
+      <c r="HI3" s="82"/>
     </row>
     <row r="4" spans="1:217" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="122">
+      <c r="B4" s="80">
         <v>0</v>
       </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="123"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="123"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="122">
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="80">
         <v>2</v>
       </c>
-      <c r="S4" s="123"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="123"/>
-      <c r="V4" s="123"/>
-      <c r="W4" s="123"/>
-      <c r="X4" s="123"/>
-      <c r="Y4" s="123"/>
-      <c r="Z4" s="123"/>
-      <c r="AA4" s="123"/>
-      <c r="AB4" s="123"/>
-      <c r="AC4" s="123"/>
-      <c r="AD4" s="123"/>
-      <c r="AE4" s="123"/>
-      <c r="AF4" s="123"/>
-      <c r="AG4" s="124"/>
-      <c r="AH4" s="122">
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="81"/>
+      <c r="AC4" s="81"/>
+      <c r="AD4" s="81"/>
+      <c r="AE4" s="81"/>
+      <c r="AF4" s="81"/>
+      <c r="AG4" s="82"/>
+      <c r="AH4" s="80">
         <v>4</v>
       </c>
-      <c r="AI4" s="123"/>
-      <c r="AJ4" s="123"/>
-      <c r="AK4" s="123"/>
-      <c r="AL4" s="123"/>
-      <c r="AM4" s="123"/>
-      <c r="AN4" s="123"/>
-      <c r="AO4" s="123"/>
-      <c r="AP4" s="123"/>
-      <c r="AQ4" s="123"/>
-      <c r="AR4" s="123"/>
-      <c r="AS4" s="123"/>
-      <c r="AT4" s="123"/>
-      <c r="AU4" s="123"/>
-      <c r="AV4" s="123"/>
-      <c r="AW4" s="124"/>
-      <c r="AX4" s="122">
+      <c r="AI4" s="81"/>
+      <c r="AJ4" s="81"/>
+      <c r="AK4" s="81"/>
+      <c r="AL4" s="81"/>
+      <c r="AM4" s="81"/>
+      <c r="AN4" s="81"/>
+      <c r="AO4" s="81"/>
+      <c r="AP4" s="81"/>
+      <c r="AQ4" s="81"/>
+      <c r="AR4" s="81"/>
+      <c r="AS4" s="81"/>
+      <c r="AT4" s="81"/>
+      <c r="AU4" s="81"/>
+      <c r="AV4" s="81"/>
+      <c r="AW4" s="82"/>
+      <c r="AX4" s="80">
         <v>6</v>
       </c>
-      <c r="AY4" s="123"/>
-      <c r="AZ4" s="123"/>
-      <c r="BA4" s="123"/>
-      <c r="BB4" s="123"/>
-      <c r="BC4" s="123"/>
-      <c r="BD4" s="123"/>
-      <c r="BE4" s="123"/>
-      <c r="BF4" s="123"/>
-      <c r="BG4" s="123"/>
-      <c r="BH4" s="123"/>
-      <c r="BI4" s="123"/>
-      <c r="BJ4" s="123"/>
-      <c r="BK4" s="123"/>
-      <c r="BL4" s="123"/>
-      <c r="BM4" s="124"/>
-      <c r="BN4" s="122">
+      <c r="AY4" s="81"/>
+      <c r="AZ4" s="81"/>
+      <c r="BA4" s="81"/>
+      <c r="BB4" s="81"/>
+      <c r="BC4" s="81"/>
+      <c r="BD4" s="81"/>
+      <c r="BE4" s="81"/>
+      <c r="BF4" s="81"/>
+      <c r="BG4" s="81"/>
+      <c r="BH4" s="81"/>
+      <c r="BI4" s="81"/>
+      <c r="BJ4" s="81"/>
+      <c r="BK4" s="81"/>
+      <c r="BL4" s="81"/>
+      <c r="BM4" s="82"/>
+      <c r="BN4" s="80">
         <v>8</v>
       </c>
-      <c r="BO4" s="123"/>
-      <c r="BP4" s="123"/>
-      <c r="BQ4" s="123"/>
-      <c r="BR4" s="123"/>
-      <c r="BS4" s="123"/>
-      <c r="BT4" s="123"/>
-      <c r="BU4" s="124"/>
-      <c r="BV4" s="122">
+      <c r="BO4" s="81"/>
+      <c r="BP4" s="81"/>
+      <c r="BQ4" s="81"/>
+      <c r="BR4" s="81"/>
+      <c r="BS4" s="81"/>
+      <c r="BT4" s="81"/>
+      <c r="BU4" s="82"/>
+      <c r="BV4" s="80">
         <v>9</v>
       </c>
-      <c r="BW4" s="123"/>
-      <c r="BX4" s="123"/>
-      <c r="BY4" s="123"/>
-      <c r="BZ4" s="123"/>
-      <c r="CA4" s="123"/>
-      <c r="CB4" s="123"/>
-      <c r="CC4" s="124"/>
-      <c r="CD4" s="122" t="str">
+      <c r="BW4" s="81"/>
+      <c r="BX4" s="81"/>
+      <c r="BY4" s="81"/>
+      <c r="BZ4" s="81"/>
+      <c r="CA4" s="81"/>
+      <c r="CB4" s="81"/>
+      <c r="CC4" s="82"/>
+      <c r="CD4" s="80" t="str">
         <f>CD3</f>
         <v>A</v>
       </c>
-      <c r="CE4" s="123"/>
-      <c r="CF4" s="123"/>
-      <c r="CG4" s="123"/>
-      <c r="CH4" s="123"/>
-      <c r="CI4" s="123"/>
-      <c r="CJ4" s="123"/>
-      <c r="CK4" s="124"/>
-      <c r="CL4" s="122" t="str">
+      <c r="CE4" s="81"/>
+      <c r="CF4" s="81"/>
+      <c r="CG4" s="81"/>
+      <c r="CH4" s="81"/>
+      <c r="CI4" s="81"/>
+      <c r="CJ4" s="81"/>
+      <c r="CK4" s="82"/>
+      <c r="CL4" s="80" t="str">
         <f>CL3</f>
         <v>B</v>
       </c>
-      <c r="CM4" s="123"/>
-      <c r="CN4" s="123"/>
-      <c r="CO4" s="123"/>
-      <c r="CP4" s="123"/>
-      <c r="CQ4" s="123"/>
-      <c r="CR4" s="123"/>
-      <c r="CS4" s="123"/>
-      <c r="CT4" s="123"/>
-      <c r="CU4" s="123"/>
-      <c r="CV4" s="123"/>
-      <c r="CW4" s="123"/>
-      <c r="CX4" s="123"/>
-      <c r="CY4" s="123"/>
-      <c r="CZ4" s="123"/>
-      <c r="DA4" s="124"/>
-      <c r="DB4" s="122" t="str">
+      <c r="CM4" s="81"/>
+      <c r="CN4" s="81"/>
+      <c r="CO4" s="81"/>
+      <c r="CP4" s="81"/>
+      <c r="CQ4" s="81"/>
+      <c r="CR4" s="81"/>
+      <c r="CS4" s="81"/>
+      <c r="CT4" s="81"/>
+      <c r="CU4" s="81"/>
+      <c r="CV4" s="81"/>
+      <c r="CW4" s="81"/>
+      <c r="CX4" s="81"/>
+      <c r="CY4" s="81"/>
+      <c r="CZ4" s="81"/>
+      <c r="DA4" s="82"/>
+      <c r="DB4" s="80" t="str">
         <f>DB3</f>
         <v>D</v>
       </c>
-      <c r="DC4" s="123"/>
-      <c r="DD4" s="123"/>
-      <c r="DE4" s="123"/>
-      <c r="DF4" s="123"/>
-      <c r="DG4" s="123"/>
-      <c r="DH4" s="123"/>
-      <c r="DI4" s="123"/>
-      <c r="DJ4" s="123"/>
-      <c r="DK4" s="123"/>
-      <c r="DL4" s="123"/>
-      <c r="DM4" s="123"/>
-      <c r="DN4" s="123"/>
-      <c r="DO4" s="123"/>
-      <c r="DP4" s="123"/>
-      <c r="DQ4" s="124"/>
-      <c r="DR4" s="122" t="str">
+      <c r="DC4" s="81"/>
+      <c r="DD4" s="81"/>
+      <c r="DE4" s="81"/>
+      <c r="DF4" s="81"/>
+      <c r="DG4" s="81"/>
+      <c r="DH4" s="81"/>
+      <c r="DI4" s="81"/>
+      <c r="DJ4" s="81"/>
+      <c r="DK4" s="81"/>
+      <c r="DL4" s="81"/>
+      <c r="DM4" s="81"/>
+      <c r="DN4" s="81"/>
+      <c r="DO4" s="81"/>
+      <c r="DP4" s="81"/>
+      <c r="DQ4" s="82"/>
+      <c r="DR4" s="80" t="str">
         <f t="shared" ref="DR4" si="26">DR3</f>
         <v>F</v>
       </c>
-      <c r="DS4" s="123"/>
-      <c r="DT4" s="123"/>
-      <c r="DU4" s="123"/>
-      <c r="DV4" s="123"/>
-      <c r="DW4" s="123"/>
-      <c r="DX4" s="123"/>
-      <c r="DY4" s="123"/>
-      <c r="DZ4" s="123"/>
-      <c r="EA4" s="123"/>
-      <c r="EB4" s="123"/>
-      <c r="EC4" s="123"/>
-      <c r="ED4" s="123"/>
-      <c r="EE4" s="123"/>
-      <c r="EF4" s="123"/>
-      <c r="EG4" s="124"/>
-      <c r="EH4" s="122" t="str">
+      <c r="DS4" s="81"/>
+      <c r="DT4" s="81"/>
+      <c r="DU4" s="81"/>
+      <c r="DV4" s="81"/>
+      <c r="DW4" s="81"/>
+      <c r="DX4" s="81"/>
+      <c r="DY4" s="81"/>
+      <c r="DZ4" s="81"/>
+      <c r="EA4" s="81"/>
+      <c r="EB4" s="81"/>
+      <c r="EC4" s="81"/>
+      <c r="ED4" s="81"/>
+      <c r="EE4" s="81"/>
+      <c r="EF4" s="81"/>
+      <c r="EG4" s="82"/>
+      <c r="EH4" s="80" t="str">
         <f t="shared" ref="EH4" si="27">EH3</f>
         <v>11</v>
       </c>
-      <c r="EI4" s="123"/>
-      <c r="EJ4" s="123"/>
-      <c r="EK4" s="123"/>
-      <c r="EL4" s="123"/>
-      <c r="EM4" s="123"/>
-      <c r="EN4" s="123"/>
-      <c r="EO4" s="124"/>
-      <c r="EP4" s="122" t="str">
+      <c r="EI4" s="81"/>
+      <c r="EJ4" s="81"/>
+      <c r="EK4" s="81"/>
+      <c r="EL4" s="81"/>
+      <c r="EM4" s="81"/>
+      <c r="EN4" s="81"/>
+      <c r="EO4" s="82"/>
+      <c r="EP4" s="80" t="str">
         <f t="shared" ref="EP4" si="28">EP3</f>
         <v>12</v>
       </c>
-      <c r="EQ4" s="123"/>
-      <c r="ER4" s="123"/>
-      <c r="ES4" s="123"/>
-      <c r="ET4" s="123"/>
-      <c r="EU4" s="123"/>
-      <c r="EV4" s="123"/>
-      <c r="EW4" s="124"/>
-      <c r="EX4" s="122" t="str">
+      <c r="EQ4" s="81"/>
+      <c r="ER4" s="81"/>
+      <c r="ES4" s="81"/>
+      <c r="ET4" s="81"/>
+      <c r="EU4" s="81"/>
+      <c r="EV4" s="81"/>
+      <c r="EW4" s="82"/>
+      <c r="EX4" s="80" t="str">
         <f t="shared" ref="EX4" si="29">EX3</f>
         <v>13</v>
       </c>
-      <c r="EY4" s="123"/>
-      <c r="EZ4" s="123"/>
-      <c r="FA4" s="123"/>
-      <c r="FB4" s="123"/>
-      <c r="FC4" s="123"/>
-      <c r="FD4" s="123"/>
-      <c r="FE4" s="124"/>
-      <c r="FF4" s="122" t="str">
+      <c r="EY4" s="81"/>
+      <c r="EZ4" s="81"/>
+      <c r="FA4" s="81"/>
+      <c r="FB4" s="81"/>
+      <c r="FC4" s="81"/>
+      <c r="FD4" s="81"/>
+      <c r="FE4" s="82"/>
+      <c r="FF4" s="80" t="str">
         <f t="shared" ref="FF4" si="30">FF3</f>
         <v>14</v>
       </c>
-      <c r="FG4" s="123"/>
-      <c r="FH4" s="123"/>
-      <c r="FI4" s="123"/>
-      <c r="FJ4" s="123"/>
-      <c r="FK4" s="123"/>
-      <c r="FL4" s="123"/>
-      <c r="FM4" s="124"/>
-      <c r="FN4" s="122" t="str">
+      <c r="FG4" s="81"/>
+      <c r="FH4" s="81"/>
+      <c r="FI4" s="81"/>
+      <c r="FJ4" s="81"/>
+      <c r="FK4" s="81"/>
+      <c r="FL4" s="81"/>
+      <c r="FM4" s="82"/>
+      <c r="FN4" s="80" t="str">
         <f t="shared" ref="FN4" si="31">FN3</f>
         <v>15</v>
       </c>
-      <c r="FO4" s="123"/>
-      <c r="FP4" s="123"/>
-      <c r="FQ4" s="123"/>
-      <c r="FR4" s="123"/>
-      <c r="FS4" s="123"/>
-      <c r="FT4" s="123"/>
-      <c r="FU4" s="124"/>
-      <c r="FV4" s="122" t="str">
+      <c r="FO4" s="81"/>
+      <c r="FP4" s="81"/>
+      <c r="FQ4" s="81"/>
+      <c r="FR4" s="81"/>
+      <c r="FS4" s="81"/>
+      <c r="FT4" s="81"/>
+      <c r="FU4" s="82"/>
+      <c r="FV4" s="80" t="str">
         <f t="shared" ref="FV4" si="32">FV3</f>
         <v>16</v>
       </c>
-      <c r="FW4" s="123"/>
-      <c r="FX4" s="123"/>
-      <c r="FY4" s="123"/>
-      <c r="FZ4" s="123"/>
-      <c r="GA4" s="123"/>
-      <c r="GB4" s="123"/>
-      <c r="GC4" s="123"/>
-      <c r="GD4" s="123"/>
-      <c r="GE4" s="123"/>
-      <c r="GF4" s="123"/>
-      <c r="GG4" s="123"/>
-      <c r="GH4" s="123"/>
-      <c r="GI4" s="123"/>
-      <c r="GJ4" s="123"/>
-      <c r="GK4" s="124"/>
-      <c r="GL4" s="122" t="str">
+      <c r="FW4" s="81"/>
+      <c r="FX4" s="81"/>
+      <c r="FY4" s="81"/>
+      <c r="FZ4" s="81"/>
+      <c r="GA4" s="81"/>
+      <c r="GB4" s="81"/>
+      <c r="GC4" s="81"/>
+      <c r="GD4" s="81"/>
+      <c r="GE4" s="81"/>
+      <c r="GF4" s="81"/>
+      <c r="GG4" s="81"/>
+      <c r="GH4" s="81"/>
+      <c r="GI4" s="81"/>
+      <c r="GJ4" s="81"/>
+      <c r="GK4" s="82"/>
+      <c r="GL4" s="80" t="str">
         <f t="shared" ref="GL4" si="33">GL3</f>
         <v>18</v>
       </c>
-      <c r="GM4" s="123"/>
-      <c r="GN4" s="123"/>
-      <c r="GO4" s="123"/>
-      <c r="GP4" s="123"/>
-      <c r="GQ4" s="123"/>
-      <c r="GR4" s="123"/>
-      <c r="GS4" s="124"/>
-      <c r="GT4" s="122" t="str">
+      <c r="GM4" s="81"/>
+      <c r="GN4" s="81"/>
+      <c r="GO4" s="81"/>
+      <c r="GP4" s="81"/>
+      <c r="GQ4" s="81"/>
+      <c r="GR4" s="81"/>
+      <c r="GS4" s="82"/>
+      <c r="GT4" s="80" t="str">
         <f t="shared" ref="GT4" si="34">GT3</f>
         <v>19</v>
       </c>
-      <c r="GU4" s="123"/>
-      <c r="GV4" s="123"/>
-      <c r="GW4" s="123"/>
-      <c r="GX4" s="123"/>
-      <c r="GY4" s="123"/>
-      <c r="GZ4" s="123"/>
-      <c r="HA4" s="124"/>
-      <c r="HB4" s="122" t="str">
+      <c r="GU4" s="81"/>
+      <c r="GV4" s="81"/>
+      <c r="GW4" s="81"/>
+      <c r="GX4" s="81"/>
+      <c r="GY4" s="81"/>
+      <c r="GZ4" s="81"/>
+      <c r="HA4" s="82"/>
+      <c r="HB4" s="80" t="str">
         <f t="shared" ref="HB4" si="35">HB3</f>
         <v>1A</v>
       </c>
-      <c r="HC4" s="123"/>
-      <c r="HD4" s="123"/>
-      <c r="HE4" s="123"/>
-      <c r="HF4" s="123"/>
-      <c r="HG4" s="123"/>
-      <c r="HH4" s="123"/>
-      <c r="HI4" s="124"/>
+      <c r="HC4" s="81"/>
+      <c r="HD4" s="81"/>
+      <c r="HE4" s="81"/>
+      <c r="HF4" s="81"/>
+      <c r="HG4" s="81"/>
+      <c r="HH4" s="81"/>
+      <c r="HI4" s="82"/>
     </row>
     <row r="5" spans="1:217" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
@@ -5026,147 +5026,147 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="125" t="s">
+      <c r="F7" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="126"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="151" t="s">
+      <c r="G7" s="115"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="151"/>
-      <c r="K7" s="151"/>
-      <c r="L7" s="151"/>
-      <c r="M7" s="151"/>
-      <c r="N7" s="151"/>
-      <c r="O7" s="151"/>
-      <c r="P7" s="151"/>
-      <c r="Q7" s="151"/>
-      <c r="R7" s="128" t="s">
+      <c r="J7" s="111"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="111"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="129"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="128" t="s">
+      <c r="S7" s="109"/>
+      <c r="T7" s="110"/>
+      <c r="U7" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="V7" s="129"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="131" t="s">
+      <c r="V7" s="109"/>
+      <c r="W7" s="110"/>
+      <c r="X7" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="Y7" s="132"/>
-      <c r="Z7" s="133"/>
-      <c r="AA7" s="128" t="s">
+      <c r="Y7" s="136"/>
+      <c r="Z7" s="137"/>
+      <c r="AA7" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="AB7" s="129"/>
-      <c r="AC7" s="129"/>
-      <c r="AD7" s="129"/>
-      <c r="AE7" s="129"/>
-      <c r="AF7" s="129"/>
-      <c r="AG7" s="130"/>
-      <c r="AH7" s="128" t="s">
+      <c r="AB7" s="109"/>
+      <c r="AC7" s="109"/>
+      <c r="AD7" s="109"/>
+      <c r="AE7" s="109"/>
+      <c r="AF7" s="109"/>
+      <c r="AG7" s="110"/>
+      <c r="AH7" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="129"/>
-      <c r="AJ7" s="129"/>
-      <c r="AK7" s="129"/>
-      <c r="AL7" s="129"/>
-      <c r="AM7" s="129"/>
-      <c r="AN7" s="129"/>
-      <c r="AO7" s="129"/>
-      <c r="AP7" s="129"/>
-      <c r="AQ7" s="130"/>
-      <c r="AR7" s="128" t="s">
+      <c r="AI7" s="109"/>
+      <c r="AJ7" s="109"/>
+      <c r="AK7" s="109"/>
+      <c r="AL7" s="109"/>
+      <c r="AM7" s="109"/>
+      <c r="AN7" s="109"/>
+      <c r="AO7" s="109"/>
+      <c r="AP7" s="109"/>
+      <c r="AQ7" s="110"/>
+      <c r="AR7" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AS7" s="129"/>
-      <c r="AT7" s="129"/>
-      <c r="AU7" s="129"/>
-      <c r="AV7" s="129"/>
-      <c r="AW7" s="130"/>
-      <c r="AX7" s="128" t="s">
+      <c r="AS7" s="109"/>
+      <c r="AT7" s="109"/>
+      <c r="AU7" s="109"/>
+      <c r="AV7" s="109"/>
+      <c r="AW7" s="110"/>
+      <c r="AX7" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="AY7" s="129"/>
-      <c r="AZ7" s="129"/>
-      <c r="BA7" s="129"/>
-      <c r="BB7" s="129"/>
-      <c r="BC7" s="129"/>
-      <c r="BD7" s="129"/>
-      <c r="BE7" s="129"/>
-      <c r="BF7" s="129"/>
-      <c r="BG7" s="130"/>
-      <c r="BH7" s="128" t="s">
+      <c r="AY7" s="109"/>
+      <c r="AZ7" s="109"/>
+      <c r="BA7" s="109"/>
+      <c r="BB7" s="109"/>
+      <c r="BC7" s="109"/>
+      <c r="BD7" s="109"/>
+      <c r="BE7" s="109"/>
+      <c r="BF7" s="109"/>
+      <c r="BG7" s="110"/>
+      <c r="BH7" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="BI7" s="129"/>
-      <c r="BJ7" s="129"/>
-      <c r="BK7" s="129"/>
-      <c r="BL7" s="129"/>
-      <c r="BM7" s="130"/>
-      <c r="BN7" s="128" t="s">
+      <c r="BI7" s="109"/>
+      <c r="BJ7" s="109"/>
+      <c r="BK7" s="109"/>
+      <c r="BL7" s="109"/>
+      <c r="BM7" s="110"/>
+      <c r="BN7" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="BO7" s="129"/>
-      <c r="BP7" s="129"/>
-      <c r="BQ7" s="129"/>
-      <c r="BR7" s="129"/>
-      <c r="BS7" s="129"/>
-      <c r="BT7" s="129"/>
-      <c r="BU7" s="130"/>
-      <c r="BV7" s="128" t="s">
+      <c r="BO7" s="109"/>
+      <c r="BP7" s="109"/>
+      <c r="BQ7" s="109"/>
+      <c r="BR7" s="109"/>
+      <c r="BS7" s="109"/>
+      <c r="BT7" s="109"/>
+      <c r="BU7" s="110"/>
+      <c r="BV7" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="BW7" s="129"/>
-      <c r="BX7" s="129"/>
-      <c r="BY7" s="129"/>
-      <c r="BZ7" s="129"/>
-      <c r="CA7" s="129"/>
-      <c r="CB7" s="129"/>
-      <c r="CC7" s="130"/>
-      <c r="CD7" s="149" t="s">
+      <c r="BW7" s="109"/>
+      <c r="BX7" s="109"/>
+      <c r="BY7" s="109"/>
+      <c r="BZ7" s="109"/>
+      <c r="CA7" s="109"/>
+      <c r="CB7" s="109"/>
+      <c r="CC7" s="110"/>
+      <c r="CD7" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="CE7" s="101"/>
-      <c r="CF7" s="101"/>
-      <c r="CG7" s="101"/>
-      <c r="CH7" s="101"/>
-      <c r="CI7" s="101"/>
-      <c r="CJ7" s="101"/>
-      <c r="CK7" s="150"/>
-      <c r="CL7" s="128" t="s">
+      <c r="CE7" s="100"/>
+      <c r="CF7" s="100"/>
+      <c r="CG7" s="100"/>
+      <c r="CH7" s="100"/>
+      <c r="CI7" s="100"/>
+      <c r="CJ7" s="100"/>
+      <c r="CK7" s="107"/>
+      <c r="CL7" s="108" t="s">
         <v>191</v>
       </c>
-      <c r="CM7" s="129"/>
-      <c r="CN7" s="129"/>
-      <c r="CO7" s="130"/>
-      <c r="CP7" s="146" t="s">
+      <c r="CM7" s="109"/>
+      <c r="CN7" s="109"/>
+      <c r="CO7" s="110"/>
+      <c r="CP7" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="CQ7" s="147"/>
-      <c r="CR7" s="147"/>
-      <c r="CS7" s="147"/>
-      <c r="CT7" s="147"/>
-      <c r="CU7" s="147"/>
-      <c r="CV7" s="147"/>
-      <c r="CW7" s="148"/>
-      <c r="CX7" s="128" t="s">
+      <c r="CQ7" s="113"/>
+      <c r="CR7" s="113"/>
+      <c r="CS7" s="113"/>
+      <c r="CT7" s="113"/>
+      <c r="CU7" s="113"/>
+      <c r="CV7" s="113"/>
+      <c r="CW7" s="114"/>
+      <c r="CX7" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="CY7" s="129"/>
-      <c r="CZ7" s="129"/>
-      <c r="DA7" s="130"/>
-      <c r="DB7" s="128" t="s">
+      <c r="CY7" s="109"/>
+      <c r="CZ7" s="109"/>
+      <c r="DA7" s="110"/>
+      <c r="DB7" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="DC7" s="130"/>
+      <c r="DC7" s="110"/>
       <c r="DD7" s="6" t="s">
         <v>28</v>
       </c>
@@ -5179,70 +5179,70 @@
       </c>
       <c r="DH7" s="28"/>
       <c r="DI7" s="28"/>
-      <c r="DJ7" s="134" t="s">
-        <v>269</v>
-      </c>
-      <c r="DK7" s="135"/>
-      <c r="DL7" s="135"/>
-      <c r="DM7" s="136"/>
-      <c r="DN7" s="126" t="s">
+      <c r="DJ7" s="87" t="s">
+        <v>268</v>
+      </c>
+      <c r="DK7" s="127"/>
+      <c r="DL7" s="127"/>
+      <c r="DM7" s="88"/>
+      <c r="DN7" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="DO7" s="126"/>
-      <c r="DP7" s="126"/>
-      <c r="DQ7" s="127"/>
-      <c r="DR7" s="137" t="s">
+      <c r="DO7" s="115"/>
+      <c r="DP7" s="115"/>
+      <c r="DQ7" s="116"/>
+      <c r="DR7" s="83" t="s">
         <v>225</v>
       </c>
-      <c r="DS7" s="138"/>
-      <c r="DT7" s="138"/>
-      <c r="DU7" s="139"/>
-      <c r="DV7" s="154" t="s">
-        <v>267</v>
-      </c>
-      <c r="DW7" s="155"/>
-      <c r="DX7" s="155"/>
-      <c r="DY7" s="155"/>
-      <c r="DZ7" s="155"/>
-      <c r="EA7" s="156"/>
-      <c r="EB7" s="157" t="s">
+      <c r="DS7" s="69"/>
+      <c r="DT7" s="69"/>
+      <c r="DU7" s="70"/>
+      <c r="DV7" s="122" t="s">
+        <v>266</v>
+      </c>
+      <c r="DW7" s="123"/>
+      <c r="DX7" s="123"/>
+      <c r="DY7" s="123"/>
+      <c r="DZ7" s="123"/>
+      <c r="EA7" s="124"/>
+      <c r="EB7" s="125" t="s">
         <v>236</v>
       </c>
-      <c r="EC7" s="155"/>
-      <c r="ED7" s="155"/>
-      <c r="EE7" s="155"/>
-      <c r="EF7" s="155"/>
-      <c r="EG7" s="156"/>
-      <c r="EH7" s="122" t="s">
+      <c r="EC7" s="123"/>
+      <c r="ED7" s="123"/>
+      <c r="EE7" s="123"/>
+      <c r="EF7" s="123"/>
+      <c r="EG7" s="124"/>
+      <c r="EH7" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="EI7" s="123"/>
-      <c r="EJ7" s="123"/>
-      <c r="EK7" s="123"/>
-      <c r="EL7" s="123"/>
-      <c r="EM7" s="123"/>
-      <c r="EN7" s="123"/>
-      <c r="EO7" s="124"/>
-      <c r="EP7" s="146" t="s">
+      <c r="EI7" s="81"/>
+      <c r="EJ7" s="81"/>
+      <c r="EK7" s="81"/>
+      <c r="EL7" s="81"/>
+      <c r="EM7" s="81"/>
+      <c r="EN7" s="81"/>
+      <c r="EO7" s="82"/>
+      <c r="EP7" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="EQ7" s="147"/>
-      <c r="ER7" s="147"/>
-      <c r="ES7" s="147"/>
-      <c r="ET7" s="147"/>
-      <c r="EU7" s="147"/>
-      <c r="EV7" s="147"/>
-      <c r="EW7" s="148"/>
+      <c r="EQ7" s="113"/>
+      <c r="ER7" s="113"/>
+      <c r="ES7" s="113"/>
+      <c r="ET7" s="113"/>
+      <c r="EU7" s="113"/>
+      <c r="EV7" s="113"/>
+      <c r="EW7" s="114"/>
       <c r="EX7" s="22"/>
-      <c r="EY7" s="134" t="s">
+      <c r="EY7" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="EZ7" s="135"/>
-      <c r="FA7" s="135"/>
-      <c r="FB7" s="135"/>
-      <c r="FC7" s="135"/>
-      <c r="FD7" s="135"/>
-      <c r="FE7" s="136"/>
+      <c r="EZ7" s="127"/>
+      <c r="FA7" s="127"/>
+      <c r="FB7" s="127"/>
+      <c r="FC7" s="127"/>
+      <c r="FD7" s="127"/>
+      <c r="FE7" s="88"/>
       <c r="FF7" s="2" t="s">
         <v>55</v>
       </c>
@@ -5252,79 +5252,79 @@
       <c r="FH7" s="24"/>
       <c r="FI7" s="24"/>
       <c r="FJ7" s="25"/>
-      <c r="FK7" s="140" t="s">
+      <c r="FK7" s="128" t="s">
         <v>33</v>
       </c>
-      <c r="FL7" s="141"/>
-      <c r="FM7" s="142"/>
+      <c r="FL7" s="129"/>
+      <c r="FM7" s="130"/>
       <c r="FN7" s="38"/>
       <c r="FO7" s="39"/>
-      <c r="FP7" s="143" t="s">
+      <c r="FP7" s="131" t="s">
         <v>190</v>
       </c>
-      <c r="FQ7" s="144"/>
-      <c r="FR7" s="144"/>
-      <c r="FS7" s="144"/>
-      <c r="FT7" s="144"/>
-      <c r="FU7" s="145"/>
-      <c r="FV7" s="138" t="s">
+      <c r="FQ7" s="132"/>
+      <c r="FR7" s="132"/>
+      <c r="FS7" s="132"/>
+      <c r="FT7" s="132"/>
+      <c r="FU7" s="133"/>
+      <c r="FV7" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="FW7" s="138"/>
-      <c r="FX7" s="138"/>
-      <c r="FY7" s="138"/>
-      <c r="FZ7" s="138"/>
-      <c r="GA7" s="139"/>
-      <c r="GB7" s="137" t="s">
+      <c r="FW7" s="69"/>
+      <c r="FX7" s="69"/>
+      <c r="FY7" s="69"/>
+      <c r="FZ7" s="69"/>
+      <c r="GA7" s="70"/>
+      <c r="GB7" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="GC7" s="138"/>
-      <c r="GD7" s="138"/>
-      <c r="GE7" s="138"/>
-      <c r="GF7" s="138"/>
-      <c r="GG7" s="139"/>
-      <c r="GH7" s="122" t="s">
+      <c r="GC7" s="69"/>
+      <c r="GD7" s="69"/>
+      <c r="GE7" s="69"/>
+      <c r="GF7" s="69"/>
+      <c r="GG7" s="70"/>
+      <c r="GH7" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="GI7" s="123"/>
-      <c r="GJ7" s="123"/>
-      <c r="GK7" s="124"/>
-      <c r="GL7" s="122" t="s">
+      <c r="GI7" s="81"/>
+      <c r="GJ7" s="81"/>
+      <c r="GK7" s="82"/>
+      <c r="GL7" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="GM7" s="123"/>
-      <c r="GN7" s="124"/>
-      <c r="GO7" s="137" t="s">
+      <c r="GM7" s="81"/>
+      <c r="GN7" s="82"/>
+      <c r="GO7" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="GP7" s="138"/>
-      <c r="GQ7" s="138"/>
-      <c r="GR7" s="138"/>
-      <c r="GS7" s="139"/>
+      <c r="GP7" s="69"/>
+      <c r="GQ7" s="69"/>
+      <c r="GR7" s="69"/>
+      <c r="GS7" s="70"/>
       <c r="GT7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="GU7" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="GV7" s="109" t="s">
+        <v>271</v>
+      </c>
+      <c r="GV7" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="GW7" s="110"/>
-      <c r="GX7" s="110"/>
-      <c r="GY7" s="110"/>
-      <c r="GZ7" s="110"/>
-      <c r="HA7" s="152"/>
-      <c r="HB7" s="137" t="s">
+      <c r="GW7" s="85"/>
+      <c r="GX7" s="85"/>
+      <c r="GY7" s="85"/>
+      <c r="GZ7" s="85"/>
+      <c r="HA7" s="86"/>
+      <c r="HB7" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="HC7" s="138"/>
-      <c r="HD7" s="138"/>
-      <c r="HE7" s="138"/>
-      <c r="HF7" s="138"/>
-      <c r="HG7" s="138"/>
-      <c r="HH7" s="138"/>
-      <c r="HI7" s="139"/>
+      <c r="HC7" s="69"/>
+      <c r="HD7" s="69"/>
+      <c r="HE7" s="69"/>
+      <c r="HF7" s="69"/>
+      <c r="HG7" s="69"/>
+      <c r="HH7" s="69"/>
+      <c r="HI7" s="70"/>
     </row>
     <row r="8" spans="1:217" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="7" t="s">
@@ -5333,23 +5333,23 @@
       <c r="B8" s="60"/>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
-      <c r="E8" s="138" t="s">
+      <c r="E8" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="138"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="139"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="70"/>
       <c r="R8" t="s">
         <v>126</v>
       </c>
       <c r="U8" t="s">
         <v>125</v>
       </c>
-      <c r="X8" s="134">
+      <c r="X8" s="87">
         <v>380</v>
       </c>
-      <c r="Y8" s="135"/>
-      <c r="Z8" s="136"/>
+      <c r="Y8" s="127"/>
+      <c r="Z8" s="88"/>
       <c r="AD8" t="s">
         <v>117</v>
       </c>
@@ -5376,24 +5376,24 @@
       <c r="CI8" s="44"/>
       <c r="CJ8" s="44"/>
       <c r="CK8" s="45"/>
-      <c r="CL8" s="152" t="s">
+      <c r="CL8" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="CM8" s="153"/>
-      <c r="CN8" s="153"/>
-      <c r="CO8" s="153"/>
-      <c r="CP8" s="153"/>
-      <c r="CQ8" s="153"/>
-      <c r="CR8" s="153"/>
-      <c r="CS8" s="153"/>
-      <c r="CT8" s="153"/>
-      <c r="CU8" s="153"/>
-      <c r="CV8" s="153"/>
-      <c r="CW8" s="153"/>
-      <c r="CX8" s="153"/>
-      <c r="CY8" s="153"/>
-      <c r="CZ8" s="153"/>
-      <c r="DA8" s="153"/>
+      <c r="CM8" s="121"/>
+      <c r="CN8" s="121"/>
+      <c r="CO8" s="121"/>
+      <c r="CP8" s="121"/>
+      <c r="CQ8" s="121"/>
+      <c r="CR8" s="121"/>
+      <c r="CS8" s="121"/>
+      <c r="CT8" s="121"/>
+      <c r="CU8" s="121"/>
+      <c r="CV8" s="121"/>
+      <c r="CW8" s="121"/>
+      <c r="CX8" s="121"/>
+      <c r="CY8" s="121"/>
+      <c r="CZ8" s="121"/>
+      <c r="DA8" s="121"/>
       <c r="DB8" s="3"/>
       <c r="DC8" s="3"/>
       <c r="DD8" s="3"/>
@@ -5402,8 +5402,8 @@
       <c r="DG8" s="4"/>
       <c r="DH8" s="3"/>
       <c r="DI8" s="3"/>
-      <c r="DJ8" s="120" t="s">
-        <v>273</v>
+      <c r="DJ8" s="148" t="s">
+        <v>272</v>
       </c>
       <c r="DK8" s="104"/>
       <c r="DL8" s="104"/>
@@ -5411,35 +5411,35 @@
       <c r="DN8" s="104"/>
       <c r="DO8" s="104"/>
       <c r="DP8" s="104"/>
-      <c r="DQ8" s="121"/>
-      <c r="DR8" s="153" t="s">
+      <c r="DQ8" s="149"/>
+      <c r="DR8" s="121" t="s">
         <v>226</v>
       </c>
-      <c r="DS8" s="153"/>
-      <c r="DT8" s="153"/>
-      <c r="DU8" s="153"/>
-      <c r="DV8" s="153"/>
-      <c r="DW8" s="153"/>
-      <c r="DX8" s="153"/>
-      <c r="DY8" s="153"/>
-      <c r="DZ8" s="153"/>
-      <c r="EA8" s="153"/>
-      <c r="EB8" s="153"/>
-      <c r="EC8" s="153"/>
-      <c r="ED8" s="153"/>
-      <c r="EE8" s="153"/>
-      <c r="EF8" s="153"/>
-      <c r="EG8" s="153"/>
-      <c r="EH8" s="109" t="s">
+      <c r="DS8" s="121"/>
+      <c r="DT8" s="121"/>
+      <c r="DU8" s="121"/>
+      <c r="DV8" s="121"/>
+      <c r="DW8" s="121"/>
+      <c r="DX8" s="121"/>
+      <c r="DY8" s="121"/>
+      <c r="DZ8" s="121"/>
+      <c r="EA8" s="121"/>
+      <c r="EB8" s="121"/>
+      <c r="EC8" s="121"/>
+      <c r="ED8" s="121"/>
+      <c r="EE8" s="121"/>
+      <c r="EF8" s="121"/>
+      <c r="EG8" s="121"/>
+      <c r="EH8" s="84" t="s">
         <v>217</v>
       </c>
-      <c r="EI8" s="110"/>
-      <c r="EJ8" s="110"/>
-      <c r="EK8" s="110"/>
-      <c r="EL8" s="110"/>
-      <c r="EM8" s="110"/>
-      <c r="EN8" s="110"/>
-      <c r="EO8" s="110"/>
+      <c r="EI8" s="85"/>
+      <c r="EJ8" s="85"/>
+      <c r="EK8" s="85"/>
+      <c r="EL8" s="85"/>
+      <c r="EM8" s="85"/>
+      <c r="EN8" s="85"/>
+      <c r="EO8" s="85"/>
       <c r="FH8" t="s">
         <v>118</v>
       </c>
@@ -5461,10 +5461,10 @@
       </c>
       <c r="GV8" s="22"/>
       <c r="GW8" s="22"/>
-      <c r="GX8" s="134" t="s">
-        <v>271</v>
-      </c>
-      <c r="GY8" s="136"/>
+      <c r="GX8" s="87" t="s">
+        <v>270</v>
+      </c>
+      <c r="GY8" s="88"/>
       <c r="GZ8" s="22"/>
       <c r="HA8" s="22"/>
       <c r="HI8" s="15"/>
@@ -5476,14 +5476,14 @@
       <c r="B9" s="62"/>
       <c r="C9" s="63"/>
       <c r="D9" s="63" t="s">
-        <v>256</v>
-      </c>
-      <c r="E9" s="162" t="s">
-        <v>251</v>
-      </c>
-      <c r="F9" s="158"/>
-      <c r="G9" s="158"/>
-      <c r="H9" s="159"/>
+        <v>255</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="73"/>
       <c r="I9" s="98" t="s">
         <v>45</v>
       </c>
@@ -5495,71 +5495,71 @@
       <c r="O9" s="98"/>
       <c r="P9" s="98"/>
       <c r="Q9" s="99"/>
-      <c r="R9" s="90" t="s">
+      <c r="R9" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="S9" s="91"/>
-      <c r="T9" s="92"/>
-      <c r="U9" s="90" t="s">
+      <c r="S9" s="117"/>
+      <c r="T9" s="118"/>
+      <c r="U9" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="V9" s="91"/>
-      <c r="W9" s="92"/>
-      <c r="X9" s="90" t="s">
-        <v>248</v>
-      </c>
-      <c r="Y9" s="91"/>
-      <c r="Z9" s="92"/>
-      <c r="AA9" s="90" t="s">
+      <c r="V9" s="117"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="95" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y9" s="117"/>
+      <c r="Z9" s="118"/>
+      <c r="AA9" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="AB9" s="91"/>
-      <c r="AC9" s="91"/>
-      <c r="AD9" s="91"/>
-      <c r="AE9" s="91"/>
-      <c r="AF9" s="91"/>
-      <c r="AG9" s="92"/>
-      <c r="AH9" s="90" t="s">
+      <c r="AB9" s="117"/>
+      <c r="AC9" s="117"/>
+      <c r="AD9" s="117"/>
+      <c r="AE9" s="117"/>
+      <c r="AF9" s="117"/>
+      <c r="AG9" s="118"/>
+      <c r="AH9" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="AI9" s="91"/>
-      <c r="AJ9" s="91"/>
-      <c r="AK9" s="91"/>
-      <c r="AL9" s="91"/>
-      <c r="AM9" s="91"/>
-      <c r="AN9" s="91"/>
-      <c r="AO9" s="91"/>
-      <c r="AP9" s="91"/>
-      <c r="AQ9" s="92"/>
-      <c r="AR9" s="90" t="s">
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
+      <c r="AM9" s="117"/>
+      <c r="AN9" s="117"/>
+      <c r="AO9" s="117"/>
+      <c r="AP9" s="117"/>
+      <c r="AQ9" s="118"/>
+      <c r="AR9" s="95" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS9" s="117"/>
+      <c r="AT9" s="117"/>
+      <c r="AU9" s="117"/>
+      <c r="AV9" s="117"/>
+      <c r="AW9" s="118"/>
+      <c r="AX9" s="117" t="s">
+        <v>53</v>
+      </c>
+      <c r="AY9" s="117"/>
+      <c r="AZ9" s="117"/>
+      <c r="BA9" s="117"/>
+      <c r="BB9" s="117"/>
+      <c r="BC9" s="117"/>
+      <c r="BD9" s="117"/>
+      <c r="BE9" s="117"/>
+      <c r="BF9" s="117"/>
+      <c r="BG9" s="118"/>
+      <c r="BH9" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="AS9" s="91"/>
-      <c r="AT9" s="91"/>
-      <c r="AU9" s="91"/>
-      <c r="AV9" s="91"/>
-      <c r="AW9" s="92"/>
-      <c r="AX9" s="91" t="s">
-        <v>53</v>
-      </c>
-      <c r="AY9" s="91"/>
-      <c r="AZ9" s="91"/>
-      <c r="BA9" s="91"/>
-      <c r="BB9" s="91"/>
-      <c r="BC9" s="91"/>
-      <c r="BD9" s="91"/>
-      <c r="BE9" s="91"/>
-      <c r="BF9" s="91"/>
-      <c r="BG9" s="92"/>
-      <c r="BH9" s="90" t="s">
-        <v>246</v>
-      </c>
-      <c r="BI9" s="91"/>
-      <c r="BJ9" s="91"/>
-      <c r="BK9" s="91"/>
-      <c r="BL9" s="91"/>
-      <c r="BM9" s="92"/>
-      <c r="BN9" s="106" t="s">
+      <c r="BI9" s="117"/>
+      <c r="BJ9" s="117"/>
+      <c r="BK9" s="117"/>
+      <c r="BL9" s="117"/>
+      <c r="BM9" s="118"/>
+      <c r="BN9" s="164" t="s">
         <v>48</v>
       </c>
       <c r="BO9" s="98"/>
@@ -5569,7 +5569,7 @@
       <c r="BS9" s="98"/>
       <c r="BT9" s="98"/>
       <c r="BU9" s="99"/>
-      <c r="BV9" s="90" t="s">
+      <c r="BV9" s="95" t="s">
         <v>139</v>
       </c>
       <c r="BW9" s="98"/>
@@ -5580,126 +5580,126 @@
       <c r="CB9" s="98"/>
       <c r="CC9" s="99"/>
       <c r="CD9" s="57" t="s">
-        <v>262</v>
-      </c>
-      <c r="CE9" s="91" t="s">
-        <v>275</v>
-      </c>
-      <c r="CF9" s="91"/>
-      <c r="CG9" s="91"/>
-      <c r="CH9" s="91" t="s">
+        <v>261</v>
+      </c>
+      <c r="CE9" s="117" t="s">
+        <v>274</v>
+      </c>
+      <c r="CF9" s="117"/>
+      <c r="CG9" s="117"/>
+      <c r="CH9" s="117" t="s">
         <v>211</v>
       </c>
-      <c r="CI9" s="91"/>
-      <c r="CJ9" s="91"/>
-      <c r="CK9" s="92"/>
-      <c r="CL9" s="90" t="s">
+      <c r="CI9" s="117"/>
+      <c r="CJ9" s="117"/>
+      <c r="CK9" s="118"/>
+      <c r="CL9" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="CM9" s="91"/>
-      <c r="CN9" s="91"/>
-      <c r="CO9" s="91"/>
-      <c r="CP9" s="91"/>
-      <c r="CQ9" s="91"/>
-      <c r="CR9" s="91"/>
-      <c r="CS9" s="91"/>
-      <c r="CT9" s="91"/>
-      <c r="CU9" s="91"/>
-      <c r="CV9" s="91"/>
-      <c r="CW9" s="91"/>
-      <c r="CX9" s="91"/>
-      <c r="CY9" s="91"/>
-      <c r="CZ9" s="91"/>
-      <c r="DA9" s="92"/>
-      <c r="DB9" s="76" t="s">
+      <c r="CM9" s="117"/>
+      <c r="CN9" s="117"/>
+      <c r="CO9" s="117"/>
+      <c r="CP9" s="117"/>
+      <c r="CQ9" s="117"/>
+      <c r="CR9" s="117"/>
+      <c r="CS9" s="117"/>
+      <c r="CT9" s="117"/>
+      <c r="CU9" s="117"/>
+      <c r="CV9" s="117"/>
+      <c r="CW9" s="117"/>
+      <c r="CX9" s="117"/>
+      <c r="CY9" s="117"/>
+      <c r="CZ9" s="117"/>
+      <c r="DA9" s="118"/>
+      <c r="DB9" s="150" t="s">
         <v>227</v>
       </c>
-      <c r="DC9" s="77"/>
-      <c r="DD9" s="88" t="s">
+      <c r="DC9" s="151"/>
+      <c r="DD9" s="162" t="s">
         <v>235</v>
       </c>
-      <c r="DE9" s="88" t="s">
-        <v>261</v>
+      <c r="DE9" s="162" t="s">
+        <v>260</v>
       </c>
       <c r="DF9" s="51"/>
-      <c r="DG9" s="82" t="s">
+      <c r="DG9" s="156" t="s">
         <v>233</v>
       </c>
       <c r="DH9" s="51"/>
       <c r="DI9" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="DJ9" s="76" t="s">
+        <v>278</v>
+      </c>
+      <c r="DJ9" s="150" t="s">
         <v>194</v>
       </c>
-      <c r="DK9" s="85"/>
-      <c r="DL9" s="85"/>
-      <c r="DM9" s="77"/>
-      <c r="DN9" s="76" t="s">
+      <c r="DK9" s="159"/>
+      <c r="DL9" s="159"/>
+      <c r="DM9" s="151"/>
+      <c r="DN9" s="150" t="s">
         <v>231</v>
       </c>
-      <c r="DO9" s="85"/>
-      <c r="DP9" s="85"/>
-      <c r="DQ9" s="77"/>
-      <c r="DR9" s="112" t="s">
+      <c r="DO9" s="159"/>
+      <c r="DP9" s="159"/>
+      <c r="DQ9" s="151"/>
+      <c r="DR9" s="142" t="s">
         <v>224</v>
       </c>
-      <c r="DS9" s="112"/>
-      <c r="DT9" s="112"/>
-      <c r="DU9" s="112"/>
-      <c r="DV9" s="90" t="s">
-        <v>268</v>
-      </c>
-      <c r="DW9" s="91"/>
-      <c r="DX9" s="91"/>
-      <c r="DY9" s="91"/>
-      <c r="DZ9" s="91"/>
-      <c r="EA9" s="92"/>
-      <c r="EB9" s="90" t="s">
+      <c r="DS9" s="142"/>
+      <c r="DT9" s="142"/>
+      <c r="DU9" s="142"/>
+      <c r="DV9" s="95" t="s">
+        <v>267</v>
+      </c>
+      <c r="DW9" s="117"/>
+      <c r="DX9" s="117"/>
+      <c r="DY9" s="117"/>
+      <c r="DZ9" s="117"/>
+      <c r="EA9" s="118"/>
+      <c r="EB9" s="95" t="s">
         <v>218</v>
       </c>
-      <c r="EC9" s="91"/>
-      <c r="ED9" s="91"/>
-      <c r="EE9" s="91"/>
-      <c r="EF9" s="91"/>
-      <c r="EG9" s="92"/>
-      <c r="EP9" s="90" t="s">
+      <c r="EC9" s="117"/>
+      <c r="ED9" s="117"/>
+      <c r="EE9" s="117"/>
+      <c r="EF9" s="117"/>
+      <c r="EG9" s="118"/>
+      <c r="EP9" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="EQ9" s="91"/>
-      <c r="ER9" s="91"/>
-      <c r="ES9" s="91"/>
-      <c r="ET9" s="91"/>
-      <c r="EU9" s="91"/>
-      <c r="EV9" s="91"/>
-      <c r="EW9" s="92"/>
-      <c r="EX9" s="90" t="s">
+      <c r="EQ9" s="117"/>
+      <c r="ER9" s="117"/>
+      <c r="ES9" s="117"/>
+      <c r="ET9" s="117"/>
+      <c r="EU9" s="117"/>
+      <c r="EV9" s="117"/>
+      <c r="EW9" s="118"/>
+      <c r="EX9" s="95" t="s">
         <v>200</v>
       </c>
-      <c r="EY9" s="91"/>
-      <c r="EZ9" s="91"/>
-      <c r="FA9" s="91"/>
-      <c r="FB9" s="91"/>
-      <c r="FC9" s="91"/>
-      <c r="FD9" s="91"/>
-      <c r="FE9" s="92"/>
+      <c r="EY9" s="117"/>
+      <c r="EZ9" s="117"/>
+      <c r="FA9" s="117"/>
+      <c r="FB9" s="117"/>
+      <c r="FC9" s="117"/>
+      <c r="FD9" s="117"/>
+      <c r="FE9" s="118"/>
       <c r="FG9" t="s">
         <v>213</v>
       </c>
-      <c r="FK9" s="115" t="s">
+      <c r="FK9" s="89" t="s">
         <v>212</v>
       </c>
-      <c r="FL9" s="115"/>
-      <c r="FM9" s="116"/>
-      <c r="FN9" s="90" t="s">
-        <v>250</v>
+      <c r="FL9" s="89"/>
+      <c r="FM9" s="145"/>
+      <c r="FN9" s="95" t="s">
+        <v>249</v>
       </c>
       <c r="FO9" s="59"/>
       <c r="FP9" s="16"/>
       <c r="FQ9" s="46"/>
       <c r="FR9" s="46"/>
       <c r="FU9" s="30"/>
-      <c r="FV9" s="91" t="s">
+      <c r="FV9" s="117" t="s">
         <v>198</v>
       </c>
       <c r="FW9" s="98"/>
@@ -5707,7 +5707,7 @@
       <c r="FY9" s="98"/>
       <c r="FZ9" s="98"/>
       <c r="GA9" s="99"/>
-      <c r="GB9" s="90" t="s">
+      <c r="GB9" s="95" t="s">
         <v>197</v>
       </c>
       <c r="GC9" s="98"/>
@@ -5715,621 +5715,621 @@
       <c r="GE9" s="98"/>
       <c r="GF9" s="98"/>
       <c r="GG9" s="99"/>
-      <c r="GH9" s="93" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI9" s="71"/>
-      <c r="GJ9" s="71"/>
-      <c r="GK9" s="71"/>
-      <c r="GL9" s="113"/>
-      <c r="GM9" s="113"/>
-      <c r="GN9" s="164" t="s">
+      <c r="GH9" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="GI9" s="78"/>
+      <c r="GJ9" s="78"/>
+      <c r="GK9" s="78"/>
+      <c r="GL9" s="91"/>
+      <c r="GM9" s="91"/>
+      <c r="GN9" s="93" t="s">
         <v>196</v>
       </c>
-      <c r="GO9" s="90" t="s">
+      <c r="GO9" s="95" t="s">
         <v>192</v>
       </c>
-      <c r="GP9" s="91"/>
-      <c r="GQ9" s="91"/>
-      <c r="GR9" s="91"/>
-      <c r="GS9" s="92"/>
-      <c r="GT9" s="90" t="s">
-        <v>270</v>
-      </c>
-      <c r="GU9" s="91"/>
-      <c r="GV9" s="91"/>
-      <c r="GW9" s="91"/>
-      <c r="GX9" s="91"/>
-      <c r="GY9" s="91"/>
-      <c r="GZ9" s="91"/>
-      <c r="HA9" s="94"/>
-      <c r="HB9" s="90" t="s">
+      <c r="GP9" s="117"/>
+      <c r="GQ9" s="117"/>
+      <c r="GR9" s="117"/>
+      <c r="GS9" s="118"/>
+      <c r="GT9" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="GU9" s="117"/>
+      <c r="GV9" s="117"/>
+      <c r="GW9" s="117"/>
+      <c r="GX9" s="117"/>
+      <c r="GY9" s="117"/>
+      <c r="GZ9" s="117"/>
+      <c r="HA9" s="97"/>
+      <c r="HB9" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="HC9" s="91"/>
-      <c r="HD9" s="91"/>
-      <c r="HE9" s="91"/>
-      <c r="HF9" s="91"/>
-      <c r="HG9" s="91"/>
-      <c r="HH9" s="91"/>
-      <c r="HI9" s="92"/>
+      <c r="HC9" s="117"/>
+      <c r="HD9" s="117"/>
+      <c r="HE9" s="117"/>
+      <c r="HF9" s="117"/>
+      <c r="HG9" s="117"/>
+      <c r="HH9" s="117"/>
+      <c r="HI9" s="118"/>
     </row>
     <row r="10" spans="1:217" ht="77.650000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
       <c r="B10" s="64"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E10" s="16"/>
-      <c r="F10" s="73" t="s">
-        <v>252</v>
-      </c>
-      <c r="G10" s="74"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="101"/>
-      <c r="J10" s="101"/>
-      <c r="K10" s="101"/>
-      <c r="L10" s="101"/>
-      <c r="M10" s="101"/>
-      <c r="N10" s="101"/>
-      <c r="O10" s="101"/>
-      <c r="P10" s="101"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="93"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="94"/>
-      <c r="U10" s="93"/>
-      <c r="V10" s="71"/>
-      <c r="W10" s="94"/>
-      <c r="X10" s="93"/>
-      <c r="Y10" s="71"/>
-      <c r="Z10" s="94"/>
-      <c r="AA10" s="93"/>
-      <c r="AB10" s="71"/>
-      <c r="AC10" s="71"/>
-      <c r="AD10" s="71"/>
-      <c r="AE10" s="71"/>
-      <c r="AF10" s="71"/>
-      <c r="AG10" s="94"/>
-      <c r="AH10" s="93"/>
-      <c r="AI10" s="71"/>
-      <c r="AJ10" s="71"/>
-      <c r="AK10" s="71"/>
-      <c r="AL10" s="71"/>
-      <c r="AM10" s="71"/>
-      <c r="AN10" s="71"/>
-      <c r="AO10" s="71"/>
-      <c r="AP10" s="71"/>
-      <c r="AQ10" s="94"/>
-      <c r="AR10" s="93"/>
-      <c r="AS10" s="71"/>
-      <c r="AT10" s="71"/>
-      <c r="AU10" s="71"/>
-      <c r="AV10" s="71"/>
-      <c r="AW10" s="94"/>
-      <c r="AX10" s="71"/>
-      <c r="AY10" s="71"/>
-      <c r="AZ10" s="71"/>
-      <c r="BA10" s="71"/>
-      <c r="BB10" s="71"/>
-      <c r="BC10" s="71"/>
-      <c r="BD10" s="71"/>
-      <c r="BE10" s="71"/>
-      <c r="BF10" s="71"/>
-      <c r="BG10" s="94"/>
-      <c r="BH10" s="93"/>
-      <c r="BI10" s="71"/>
-      <c r="BJ10" s="71"/>
-      <c r="BK10" s="71"/>
-      <c r="BL10" s="71"/>
-      <c r="BM10" s="94"/>
-      <c r="BN10" s="100"/>
-      <c r="BO10" s="101"/>
-      <c r="BP10" s="101"/>
-      <c r="BQ10" s="101"/>
-      <c r="BR10" s="101"/>
-      <c r="BS10" s="101"/>
-      <c r="BT10" s="101"/>
-      <c r="BU10" s="102"/>
-      <c r="BV10" s="100"/>
-      <c r="BW10" s="101"/>
-      <c r="BX10" s="101"/>
-      <c r="BY10" s="101"/>
-      <c r="BZ10" s="101"/>
-      <c r="CA10" s="101"/>
-      <c r="CB10" s="101"/>
-      <c r="CC10" s="102"/>
+      <c r="F10" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="G10" s="75"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100"/>
+      <c r="O10" s="100"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="101"/>
+      <c r="R10" s="77"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="97"/>
+      <c r="U10" s="77"/>
+      <c r="V10" s="78"/>
+      <c r="W10" s="97"/>
+      <c r="X10" s="77"/>
+      <c r="Y10" s="78"/>
+      <c r="Z10" s="97"/>
+      <c r="AA10" s="77"/>
+      <c r="AB10" s="78"/>
+      <c r="AC10" s="78"/>
+      <c r="AD10" s="78"/>
+      <c r="AE10" s="78"/>
+      <c r="AF10" s="78"/>
+      <c r="AG10" s="97"/>
+      <c r="AH10" s="77"/>
+      <c r="AI10" s="78"/>
+      <c r="AJ10" s="78"/>
+      <c r="AK10" s="78"/>
+      <c r="AL10" s="78"/>
+      <c r="AM10" s="78"/>
+      <c r="AN10" s="78"/>
+      <c r="AO10" s="78"/>
+      <c r="AP10" s="78"/>
+      <c r="AQ10" s="97"/>
+      <c r="AR10" s="77"/>
+      <c r="AS10" s="78"/>
+      <c r="AT10" s="78"/>
+      <c r="AU10" s="78"/>
+      <c r="AV10" s="78"/>
+      <c r="AW10" s="97"/>
+      <c r="AX10" s="78"/>
+      <c r="AY10" s="78"/>
+      <c r="AZ10" s="78"/>
+      <c r="BA10" s="78"/>
+      <c r="BB10" s="78"/>
+      <c r="BC10" s="78"/>
+      <c r="BD10" s="78"/>
+      <c r="BE10" s="78"/>
+      <c r="BF10" s="78"/>
+      <c r="BG10" s="97"/>
+      <c r="BH10" s="77"/>
+      <c r="BI10" s="78"/>
+      <c r="BJ10" s="78"/>
+      <c r="BK10" s="78"/>
+      <c r="BL10" s="78"/>
+      <c r="BM10" s="97"/>
+      <c r="BN10" s="102"/>
+      <c r="BO10" s="100"/>
+      <c r="BP10" s="100"/>
+      <c r="BQ10" s="100"/>
+      <c r="BR10" s="100"/>
+      <c r="BS10" s="100"/>
+      <c r="BT10" s="100"/>
+      <c r="BU10" s="101"/>
+      <c r="BV10" s="102"/>
+      <c r="BW10" s="100"/>
+      <c r="BX10" s="100"/>
+      <c r="BY10" s="100"/>
+      <c r="BZ10" s="100"/>
+      <c r="CA10" s="100"/>
+      <c r="CB10" s="100"/>
+      <c r="CC10" s="101"/>
       <c r="CD10" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="CE10" s="71" t="s">
-        <v>257</v>
-      </c>
-      <c r="CF10" s="71"/>
-      <c r="CG10" s="71"/>
-      <c r="CH10" s="71" t="s">
-        <v>277</v>
-      </c>
-      <c r="CI10" s="71"/>
-      <c r="CJ10" s="71"/>
-      <c r="CK10" s="94"/>
-      <c r="CL10" s="93"/>
-      <c r="CM10" s="71"/>
-      <c r="CN10" s="71"/>
-      <c r="CO10" s="71"/>
-      <c r="CP10" s="71"/>
-      <c r="CQ10" s="71"/>
-      <c r="CR10" s="71"/>
-      <c r="CS10" s="71"/>
-      <c r="CT10" s="71"/>
-      <c r="CU10" s="71"/>
-      <c r="CV10" s="71"/>
-      <c r="CW10" s="71"/>
-      <c r="CX10" s="71"/>
-      <c r="CY10" s="71"/>
-      <c r="CZ10" s="71"/>
-      <c r="DA10" s="94"/>
-      <c r="DB10" s="78"/>
-      <c r="DC10" s="79"/>
-      <c r="DD10" s="89"/>
-      <c r="DE10" s="89"/>
+      <c r="CE10" s="78" t="s">
+        <v>256</v>
+      </c>
+      <c r="CF10" s="78"/>
+      <c r="CG10" s="78"/>
+      <c r="CH10" s="78" t="s">
+        <v>276</v>
+      </c>
+      <c r="CI10" s="78"/>
+      <c r="CJ10" s="78"/>
+      <c r="CK10" s="97"/>
+      <c r="CL10" s="77"/>
+      <c r="CM10" s="78"/>
+      <c r="CN10" s="78"/>
+      <c r="CO10" s="78"/>
+      <c r="CP10" s="78"/>
+      <c r="CQ10" s="78"/>
+      <c r="CR10" s="78"/>
+      <c r="CS10" s="78"/>
+      <c r="CT10" s="78"/>
+      <c r="CU10" s="78"/>
+      <c r="CV10" s="78"/>
+      <c r="CW10" s="78"/>
+      <c r="CX10" s="78"/>
+      <c r="CY10" s="78"/>
+      <c r="CZ10" s="78"/>
+      <c r="DA10" s="97"/>
+      <c r="DB10" s="152"/>
+      <c r="DC10" s="153"/>
+      <c r="DD10" s="163"/>
+      <c r="DE10" s="163"/>
       <c r="DF10" s="53"/>
-      <c r="DG10" s="83"/>
+      <c r="DG10" s="157"/>
       <c r="DH10" s="53"/>
       <c r="DI10" s="52"/>
-      <c r="DJ10" s="78"/>
-      <c r="DK10" s="86"/>
-      <c r="DL10" s="86"/>
-      <c r="DM10" s="79"/>
-      <c r="DN10" s="78"/>
-      <c r="DO10" s="86"/>
-      <c r="DP10" s="86"/>
-      <c r="DQ10" s="79"/>
+      <c r="DJ10" s="152"/>
+      <c r="DK10" s="160"/>
+      <c r="DL10" s="160"/>
+      <c r="DM10" s="153"/>
+      <c r="DN10" s="152"/>
+      <c r="DO10" s="160"/>
+      <c r="DP10" s="160"/>
+      <c r="DQ10" s="153"/>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16"/>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
-      <c r="DV10" s="93"/>
-      <c r="DW10" s="71"/>
-      <c r="DX10" s="71"/>
-      <c r="DY10" s="71"/>
-      <c r="DZ10" s="71"/>
-      <c r="EA10" s="94"/>
-      <c r="EB10" s="93"/>
-      <c r="EC10" s="71"/>
-      <c r="ED10" s="71"/>
-      <c r="EE10" s="71"/>
-      <c r="EF10" s="71"/>
-      <c r="EG10" s="94"/>
-      <c r="EP10" s="93"/>
-      <c r="EQ10" s="71"/>
-      <c r="ER10" s="71"/>
-      <c r="ES10" s="71"/>
-      <c r="ET10" s="71"/>
-      <c r="EU10" s="71"/>
-      <c r="EV10" s="71"/>
-      <c r="EW10" s="94"/>
+      <c r="DV10" s="77"/>
+      <c r="DW10" s="78"/>
+      <c r="DX10" s="78"/>
+      <c r="DY10" s="78"/>
+      <c r="DZ10" s="78"/>
+      <c r="EA10" s="97"/>
+      <c r="EB10" s="77"/>
+      <c r="EC10" s="78"/>
+      <c r="ED10" s="78"/>
+      <c r="EE10" s="78"/>
+      <c r="EF10" s="78"/>
+      <c r="EG10" s="97"/>
+      <c r="EP10" s="77"/>
+      <c r="EQ10" s="78"/>
+      <c r="ER10" s="78"/>
+      <c r="ES10" s="78"/>
+      <c r="ET10" s="78"/>
+      <c r="EU10" s="78"/>
+      <c r="EV10" s="78"/>
+      <c r="EW10" s="97"/>
       <c r="EX10" s="17"/>
       <c r="EY10" t="s">
         <v>204</v>
       </c>
       <c r="FE10" s="18"/>
-      <c r="FK10" s="115" t="s">
+      <c r="FK10" s="89" t="s">
         <v>209</v>
       </c>
-      <c r="FL10" s="115"/>
-      <c r="FM10" s="116"/>
-      <c r="FN10" s="95"/>
+      <c r="FL10" s="89"/>
+      <c r="FM10" s="145"/>
+      <c r="FN10" s="96"/>
       <c r="FO10" s="50"/>
       <c r="FP10" s="16"/>
       <c r="FQ10" s="16"/>
       <c r="FR10" s="16"/>
       <c r="FU10" s="30"/>
-      <c r="FV10" s="101"/>
-      <c r="FW10" s="101"/>
-      <c r="FX10" s="101"/>
-      <c r="FY10" s="101"/>
-      <c r="FZ10" s="101"/>
-      <c r="GA10" s="102"/>
-      <c r="GB10" s="100"/>
-      <c r="GC10" s="101"/>
-      <c r="GD10" s="101"/>
-      <c r="GE10" s="101"/>
-      <c r="GF10" s="101"/>
-      <c r="GG10" s="102"/>
-      <c r="GH10" s="93"/>
-      <c r="GI10" s="71"/>
-      <c r="GJ10" s="71"/>
-      <c r="GK10" s="71"/>
-      <c r="GL10" s="114"/>
-      <c r="GM10" s="114"/>
-      <c r="GN10" s="161"/>
-      <c r="GO10" s="95"/>
-      <c r="GP10" s="96"/>
-      <c r="GQ10" s="96"/>
-      <c r="GR10" s="96"/>
-      <c r="GS10" s="97"/>
-      <c r="GT10" s="93"/>
-      <c r="GU10" s="71"/>
-      <c r="GV10" s="71"/>
-      <c r="GW10" s="71"/>
-      <c r="GX10" s="71"/>
-      <c r="GY10" s="71"/>
-      <c r="GZ10" s="71"/>
-      <c r="HA10" s="94"/>
-      <c r="HB10" s="93"/>
-      <c r="HC10" s="71"/>
-      <c r="HD10" s="71"/>
-      <c r="HE10" s="71"/>
-      <c r="HF10" s="71"/>
-      <c r="HG10" s="71"/>
-      <c r="HH10" s="71"/>
-      <c r="HI10" s="94"/>
+      <c r="FV10" s="100"/>
+      <c r="FW10" s="100"/>
+      <c r="FX10" s="100"/>
+      <c r="FY10" s="100"/>
+      <c r="FZ10" s="100"/>
+      <c r="GA10" s="101"/>
+      <c r="GB10" s="102"/>
+      <c r="GC10" s="100"/>
+      <c r="GD10" s="100"/>
+      <c r="GE10" s="100"/>
+      <c r="GF10" s="100"/>
+      <c r="GG10" s="101"/>
+      <c r="GH10" s="77"/>
+      <c r="GI10" s="78"/>
+      <c r="GJ10" s="78"/>
+      <c r="GK10" s="78"/>
+      <c r="GL10" s="92"/>
+      <c r="GM10" s="92"/>
+      <c r="GN10" s="94"/>
+      <c r="GO10" s="96"/>
+      <c r="GP10" s="119"/>
+      <c r="GQ10" s="119"/>
+      <c r="GR10" s="119"/>
+      <c r="GS10" s="120"/>
+      <c r="GT10" s="77"/>
+      <c r="GU10" s="78"/>
+      <c r="GV10" s="78"/>
+      <c r="GW10" s="78"/>
+      <c r="GX10" s="78"/>
+      <c r="GY10" s="78"/>
+      <c r="GZ10" s="78"/>
+      <c r="HA10" s="97"/>
+      <c r="HB10" s="77"/>
+      <c r="HC10" s="78"/>
+      <c r="HD10" s="78"/>
+      <c r="HE10" s="78"/>
+      <c r="HF10" s="78"/>
+      <c r="HG10" s="78"/>
+      <c r="HH10" s="78"/>
+      <c r="HI10" s="97"/>
     </row>
     <row r="11" spans="1:217" ht="55.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7"/>
       <c r="B11" s="65"/>
       <c r="C11" s="66"/>
       <c r="D11" s="66" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E11" s="66"/>
       <c r="F11" s="66"/>
       <c r="G11" s="66"/>
       <c r="H11" s="67"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="101"/>
-      <c r="M11" s="101"/>
-      <c r="N11" s="101"/>
-      <c r="O11" s="101"/>
-      <c r="P11" s="101"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="93"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="94"/>
-      <c r="U11" s="93"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="94"/>
-      <c r="X11" s="93"/>
-      <c r="Y11" s="71"/>
-      <c r="Z11" s="94"/>
-      <c r="AA11" s="93"/>
-      <c r="AB11" s="71"/>
-      <c r="AC11" s="71"/>
-      <c r="AD11" s="71"/>
-      <c r="AE11" s="71"/>
-      <c r="AF11" s="71"/>
-      <c r="AG11" s="94"/>
-      <c r="AH11" s="93"/>
-      <c r="AI11" s="71"/>
-      <c r="AJ11" s="71"/>
-      <c r="AK11" s="71"/>
-      <c r="AL11" s="71"/>
-      <c r="AM11" s="71"/>
-      <c r="AN11" s="71"/>
-      <c r="AO11" s="71"/>
-      <c r="AP11" s="71"/>
-      <c r="AQ11" s="94"/>
-      <c r="AR11" s="93"/>
-      <c r="AS11" s="71"/>
-      <c r="AT11" s="71"/>
-      <c r="AU11" s="71"/>
-      <c r="AV11" s="71"/>
-      <c r="AW11" s="94"/>
-      <c r="AX11" s="71"/>
-      <c r="AY11" s="71"/>
-      <c r="AZ11" s="71"/>
-      <c r="BA11" s="71"/>
-      <c r="BB11" s="71"/>
-      <c r="BC11" s="71"/>
-      <c r="BD11" s="71"/>
-      <c r="BE11" s="71"/>
-      <c r="BF11" s="71"/>
-      <c r="BG11" s="94"/>
-      <c r="BH11" s="93"/>
-      <c r="BI11" s="71"/>
-      <c r="BJ11" s="71"/>
-      <c r="BK11" s="71"/>
-      <c r="BL11" s="71"/>
-      <c r="BM11" s="94"/>
-      <c r="BN11" s="100"/>
-      <c r="BO11" s="101"/>
-      <c r="BP11" s="101"/>
-      <c r="BQ11" s="101"/>
-      <c r="BR11" s="101"/>
-      <c r="BS11" s="101"/>
-      <c r="BT11" s="101"/>
-      <c r="BU11" s="102"/>
-      <c r="BV11" s="100"/>
-      <c r="BW11" s="101"/>
-      <c r="BX11" s="101"/>
-      <c r="BY11" s="101"/>
-      <c r="BZ11" s="101"/>
-      <c r="CA11" s="101"/>
-      <c r="CB11" s="101"/>
-      <c r="CC11" s="102"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="100"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="101"/>
+      <c r="R11" s="77"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="97"/>
+      <c r="U11" s="77"/>
+      <c r="V11" s="78"/>
+      <c r="W11" s="97"/>
+      <c r="X11" s="77"/>
+      <c r="Y11" s="78"/>
+      <c r="Z11" s="97"/>
+      <c r="AA11" s="77"/>
+      <c r="AB11" s="78"/>
+      <c r="AC11" s="78"/>
+      <c r="AD11" s="78"/>
+      <c r="AE11" s="78"/>
+      <c r="AF11" s="78"/>
+      <c r="AG11" s="97"/>
+      <c r="AH11" s="77"/>
+      <c r="AI11" s="78"/>
+      <c r="AJ11" s="78"/>
+      <c r="AK11" s="78"/>
+      <c r="AL11" s="78"/>
+      <c r="AM11" s="78"/>
+      <c r="AN11" s="78"/>
+      <c r="AO11" s="78"/>
+      <c r="AP11" s="78"/>
+      <c r="AQ11" s="97"/>
+      <c r="AR11" s="77"/>
+      <c r="AS11" s="78"/>
+      <c r="AT11" s="78"/>
+      <c r="AU11" s="78"/>
+      <c r="AV11" s="78"/>
+      <c r="AW11" s="97"/>
+      <c r="AX11" s="78"/>
+      <c r="AY11" s="78"/>
+      <c r="AZ11" s="78"/>
+      <c r="BA11" s="78"/>
+      <c r="BB11" s="78"/>
+      <c r="BC11" s="78"/>
+      <c r="BD11" s="78"/>
+      <c r="BE11" s="78"/>
+      <c r="BF11" s="78"/>
+      <c r="BG11" s="97"/>
+      <c r="BH11" s="77"/>
+      <c r="BI11" s="78"/>
+      <c r="BJ11" s="78"/>
+      <c r="BK11" s="78"/>
+      <c r="BL11" s="78"/>
+      <c r="BM11" s="97"/>
+      <c r="BN11" s="102"/>
+      <c r="BO11" s="100"/>
+      <c r="BP11" s="100"/>
+      <c r="BQ11" s="100"/>
+      <c r="BR11" s="100"/>
+      <c r="BS11" s="100"/>
+      <c r="BT11" s="100"/>
+      <c r="BU11" s="101"/>
+      <c r="BV11" s="102"/>
+      <c r="BW11" s="100"/>
+      <c r="BX11" s="100"/>
+      <c r="BY11" s="100"/>
+      <c r="BZ11" s="100"/>
+      <c r="CA11" s="100"/>
+      <c r="CB11" s="100"/>
+      <c r="CC11" s="101"/>
       <c r="CD11" s="56" t="s">
-        <v>239</v>
-      </c>
-      <c r="CE11" s="71" t="s">
-        <v>276</v>
-      </c>
-      <c r="CF11" s="71"/>
-      <c r="CG11" s="71"/>
-      <c r="CH11" s="71" t="s">
-        <v>278</v>
-      </c>
-      <c r="CI11" s="71"/>
-      <c r="CJ11" s="71"/>
-      <c r="CK11" s="94"/>
-      <c r="CL11" s="93"/>
-      <c r="CM11" s="71"/>
-      <c r="CN11" s="71"/>
-      <c r="CO11" s="71"/>
-      <c r="CP11" s="71"/>
-      <c r="CQ11" s="71"/>
-      <c r="CR11" s="71"/>
-      <c r="CS11" s="71"/>
-      <c r="CT11" s="71"/>
-      <c r="CU11" s="71"/>
-      <c r="CV11" s="71"/>
-      <c r="CW11" s="71"/>
-      <c r="CX11" s="71"/>
-      <c r="CY11" s="71"/>
-      <c r="CZ11" s="71"/>
-      <c r="DA11" s="94"/>
-      <c r="DB11" s="78"/>
-      <c r="DC11" s="79"/>
-      <c r="DD11" s="89"/>
-      <c r="DE11" s="89"/>
+        <v>238</v>
+      </c>
+      <c r="CE11" s="78" t="s">
+        <v>275</v>
+      </c>
+      <c r="CF11" s="78"/>
+      <c r="CG11" s="78"/>
+      <c r="CH11" s="78" t="s">
+        <v>277</v>
+      </c>
+      <c r="CI11" s="78"/>
+      <c r="CJ11" s="78"/>
+      <c r="CK11" s="97"/>
+      <c r="CL11" s="77"/>
+      <c r="CM11" s="78"/>
+      <c r="CN11" s="78"/>
+      <c r="CO11" s="78"/>
+      <c r="CP11" s="78"/>
+      <c r="CQ11" s="78"/>
+      <c r="CR11" s="78"/>
+      <c r="CS11" s="78"/>
+      <c r="CT11" s="78"/>
+      <c r="CU11" s="78"/>
+      <c r="CV11" s="78"/>
+      <c r="CW11" s="78"/>
+      <c r="CX11" s="78"/>
+      <c r="CY11" s="78"/>
+      <c r="CZ11" s="78"/>
+      <c r="DA11" s="97"/>
+      <c r="DB11" s="152"/>
+      <c r="DC11" s="153"/>
+      <c r="DD11" s="163"/>
+      <c r="DE11" s="163"/>
       <c r="DF11" s="52"/>
-      <c r="DG11" s="83"/>
+      <c r="DG11" s="157"/>
       <c r="DH11" s="52"/>
       <c r="DI11" s="52"/>
-      <c r="DJ11" s="78"/>
-      <c r="DK11" s="86"/>
-      <c r="DL11" s="86"/>
-      <c r="DM11" s="79"/>
-      <c r="DN11" s="78"/>
-      <c r="DO11" s="86"/>
-      <c r="DP11" s="86"/>
-      <c r="DQ11" s="79"/>
-      <c r="DR11" s="158" t="s">
+      <c r="DJ11" s="152"/>
+      <c r="DK11" s="160"/>
+      <c r="DL11" s="160"/>
+      <c r="DM11" s="153"/>
+      <c r="DN11" s="152"/>
+      <c r="DO11" s="160"/>
+      <c r="DP11" s="160"/>
+      <c r="DQ11" s="153"/>
+      <c r="DR11" s="72" t="s">
         <v>223</v>
       </c>
-      <c r="DS11" s="158"/>
-      <c r="DT11" s="158"/>
-      <c r="DU11" s="158"/>
-      <c r="DV11" s="158"/>
-      <c r="DW11" s="158"/>
-      <c r="DX11" s="158"/>
-      <c r="DY11" s="158"/>
-      <c r="DZ11" s="158"/>
-      <c r="EA11" s="158"/>
-      <c r="EB11" s="158"/>
-      <c r="EC11" s="158"/>
-      <c r="ED11" s="158"/>
-      <c r="EE11" s="158"/>
-      <c r="EF11" s="158"/>
-      <c r="EG11" s="159"/>
-      <c r="EH11" s="71" t="s">
+      <c r="DS11" s="72"/>
+      <c r="DT11" s="72"/>
+      <c r="DU11" s="72"/>
+      <c r="DV11" s="72"/>
+      <c r="DW11" s="72"/>
+      <c r="DX11" s="72"/>
+      <c r="DY11" s="72"/>
+      <c r="DZ11" s="72"/>
+      <c r="EA11" s="72"/>
+      <c r="EB11" s="72"/>
+      <c r="EC11" s="72"/>
+      <c r="ED11" s="72"/>
+      <c r="EE11" s="72"/>
+      <c r="EF11" s="72"/>
+      <c r="EG11" s="73"/>
+      <c r="EH11" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="EI11" s="71"/>
-      <c r="EJ11" s="71"/>
-      <c r="EK11" s="71"/>
-      <c r="EL11" s="71"/>
-      <c r="EM11" s="71"/>
-      <c r="EN11" s="71"/>
-      <c r="EO11" s="94"/>
-      <c r="EP11" s="93"/>
-      <c r="EQ11" s="71"/>
-      <c r="ER11" s="71"/>
-      <c r="ES11" s="71"/>
-      <c r="ET11" s="71"/>
-      <c r="EU11" s="71"/>
-      <c r="EV11" s="71"/>
-      <c r="EW11" s="94"/>
+      <c r="EI11" s="78"/>
+      <c r="EJ11" s="78"/>
+      <c r="EK11" s="78"/>
+      <c r="EL11" s="78"/>
+      <c r="EM11" s="78"/>
+      <c r="EN11" s="78"/>
+      <c r="EO11" s="97"/>
+      <c r="EP11" s="77"/>
+      <c r="EQ11" s="78"/>
+      <c r="ER11" s="78"/>
+      <c r="ES11" s="78"/>
+      <c r="ET11" s="78"/>
+      <c r="EU11" s="78"/>
+      <c r="EV11" s="78"/>
+      <c r="EW11" s="97"/>
       <c r="EX11" s="47" t="s">
         <v>208</v>
       </c>
-      <c r="EY11" s="93" t="s">
+      <c r="EY11" s="77" t="s">
         <v>206</v>
       </c>
-      <c r="EZ11" s="71"/>
-      <c r="FA11" s="71"/>
-      <c r="FB11" s="71"/>
-      <c r="FC11" s="71"/>
-      <c r="FD11" s="71"/>
-      <c r="FE11" s="94"/>
-      <c r="FF11" s="93" t="s">
+      <c r="EZ11" s="78"/>
+      <c r="FA11" s="78"/>
+      <c r="FB11" s="78"/>
+      <c r="FC11" s="78"/>
+      <c r="FD11" s="78"/>
+      <c r="FE11" s="97"/>
+      <c r="FF11" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="FG11" s="71"/>
-      <c r="FH11" s="71"/>
-      <c r="FI11" s="71"/>
-      <c r="FJ11" s="71"/>
-      <c r="FK11" s="115" t="s">
+      <c r="FG11" s="78"/>
+      <c r="FH11" s="78"/>
+      <c r="FI11" s="78"/>
+      <c r="FJ11" s="78"/>
+      <c r="FK11" s="89" t="s">
         <v>210</v>
       </c>
-      <c r="FL11" s="115"/>
-      <c r="FM11" s="117"/>
-      <c r="FN11" s="70" t="s">
-        <v>258</v>
-      </c>
-      <c r="FO11" s="72"/>
-      <c r="FP11" s="70" t="s">
+      <c r="FL11" s="89"/>
+      <c r="FM11" s="90"/>
+      <c r="FN11" s="143" t="s">
+        <v>257</v>
+      </c>
+      <c r="FO11" s="144"/>
+      <c r="FP11" s="143" t="s">
         <v>203</v>
       </c>
-      <c r="FQ11" s="71"/>
-      <c r="FR11" s="71"/>
-      <c r="FS11" s="71"/>
-      <c r="FT11" s="71"/>
-      <c r="FU11" s="72"/>
-      <c r="FV11" s="101"/>
-      <c r="FW11" s="101"/>
-      <c r="FX11" s="101"/>
-      <c r="FY11" s="101"/>
-      <c r="FZ11" s="101"/>
-      <c r="GA11" s="102"/>
-      <c r="GB11" s="100"/>
-      <c r="GC11" s="101"/>
-      <c r="GD11" s="101"/>
-      <c r="GE11" s="101"/>
-      <c r="GF11" s="101"/>
-      <c r="GG11" s="102"/>
-      <c r="GH11" s="93"/>
-      <c r="GI11" s="71"/>
-      <c r="GJ11" s="71"/>
-      <c r="GK11" s="71"/>
-      <c r="GL11" s="91" t="s">
+      <c r="FQ11" s="78"/>
+      <c r="FR11" s="78"/>
+      <c r="FS11" s="78"/>
+      <c r="FT11" s="78"/>
+      <c r="FU11" s="144"/>
+      <c r="FV11" s="100"/>
+      <c r="FW11" s="100"/>
+      <c r="FX11" s="100"/>
+      <c r="FY11" s="100"/>
+      <c r="FZ11" s="100"/>
+      <c r="GA11" s="101"/>
+      <c r="GB11" s="102"/>
+      <c r="GC11" s="100"/>
+      <c r="GD11" s="100"/>
+      <c r="GE11" s="100"/>
+      <c r="GF11" s="100"/>
+      <c r="GG11" s="101"/>
+      <c r="GH11" s="77"/>
+      <c r="GI11" s="78"/>
+      <c r="GJ11" s="78"/>
+      <c r="GK11" s="78"/>
+      <c r="GL11" s="117" t="s">
         <v>195</v>
       </c>
-      <c r="GM11" s="91"/>
-      <c r="GN11" s="91"/>
-      <c r="GT11" s="93"/>
-      <c r="GU11" s="71"/>
-      <c r="GV11" s="71"/>
-      <c r="GW11" s="71"/>
-      <c r="GX11" s="71"/>
-      <c r="GY11" s="71"/>
-      <c r="GZ11" s="71"/>
-      <c r="HA11" s="94"/>
-      <c r="HB11" s="93"/>
-      <c r="HC11" s="71"/>
-      <c r="HD11" s="71"/>
-      <c r="HE11" s="71"/>
-      <c r="HF11" s="71"/>
-      <c r="HG11" s="71"/>
-      <c r="HH11" s="71"/>
-      <c r="HI11" s="94"/>
+      <c r="GM11" s="117"/>
+      <c r="GN11" s="117"/>
+      <c r="GT11" s="77"/>
+      <c r="GU11" s="78"/>
+      <c r="GV11" s="78"/>
+      <c r="GW11" s="78"/>
+      <c r="GX11" s="78"/>
+      <c r="GY11" s="78"/>
+      <c r="GZ11" s="78"/>
+      <c r="HA11" s="97"/>
+      <c r="HB11" s="77"/>
+      <c r="HC11" s="78"/>
+      <c r="HD11" s="78"/>
+      <c r="HE11" s="78"/>
+      <c r="HF11" s="78"/>
+      <c r="HG11" s="78"/>
+      <c r="HH11" s="78"/>
+      <c r="HI11" s="97"/>
     </row>
     <row r="12" spans="1:217" ht="88.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="7"/>
       <c r="B12" s="47"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="48"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="102"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="94"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="71"/>
-      <c r="W12" s="94"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="94"/>
-      <c r="AA12" s="93"/>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="71"/>
-      <c r="AD12" s="71"/>
-      <c r="AE12" s="71"/>
-      <c r="AF12" s="71"/>
-      <c r="AG12" s="94"/>
-      <c r="AH12" s="93"/>
-      <c r="AI12" s="71"/>
-      <c r="AJ12" s="71"/>
-      <c r="AK12" s="71"/>
-      <c r="AL12" s="71"/>
-      <c r="AM12" s="71"/>
-      <c r="AN12" s="71"/>
-      <c r="AO12" s="71"/>
-      <c r="AP12" s="71"/>
-      <c r="AQ12" s="94"/>
-      <c r="AR12" s="93"/>
-      <c r="AS12" s="71"/>
-      <c r="AT12" s="71"/>
-      <c r="AU12" s="71"/>
-      <c r="AV12" s="71"/>
-      <c r="AW12" s="94"/>
-      <c r="AX12" s="71"/>
-      <c r="AY12" s="71"/>
-      <c r="AZ12" s="71"/>
-      <c r="BA12" s="71"/>
-      <c r="BB12" s="71"/>
-      <c r="BC12" s="71"/>
-      <c r="BD12" s="71"/>
-      <c r="BE12" s="71"/>
-      <c r="BF12" s="71"/>
-      <c r="BG12" s="94"/>
-      <c r="BH12" s="93"/>
-      <c r="BI12" s="71"/>
-      <c r="BJ12" s="71"/>
-      <c r="BK12" s="71"/>
-      <c r="BL12" s="71"/>
-      <c r="BM12" s="94"/>
-      <c r="BN12" s="100"/>
-      <c r="BO12" s="101"/>
-      <c r="BP12" s="101"/>
-      <c r="BQ12" s="101"/>
-      <c r="BR12" s="101"/>
-      <c r="BS12" s="101"/>
-      <c r="BT12" s="101"/>
-      <c r="BU12" s="102"/>
-      <c r="BV12" s="100"/>
-      <c r="BW12" s="101"/>
-      <c r="BX12" s="101"/>
-      <c r="BY12" s="101"/>
-      <c r="BZ12" s="101"/>
-      <c r="CA12" s="101"/>
-      <c r="CB12" s="101"/>
-      <c r="CC12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="100"/>
+      <c r="O12" s="100"/>
+      <c r="P12" s="100"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="77"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="97"/>
+      <c r="U12" s="77"/>
+      <c r="V12" s="78"/>
+      <c r="W12" s="97"/>
+      <c r="X12" s="77"/>
+      <c r="Y12" s="78"/>
+      <c r="Z12" s="97"/>
+      <c r="AA12" s="77"/>
+      <c r="AB12" s="78"/>
+      <c r="AC12" s="78"/>
+      <c r="AD12" s="78"/>
+      <c r="AE12" s="78"/>
+      <c r="AF12" s="78"/>
+      <c r="AG12" s="97"/>
+      <c r="AH12" s="77"/>
+      <c r="AI12" s="78"/>
+      <c r="AJ12" s="78"/>
+      <c r="AK12" s="78"/>
+      <c r="AL12" s="78"/>
+      <c r="AM12" s="78"/>
+      <c r="AN12" s="78"/>
+      <c r="AO12" s="78"/>
+      <c r="AP12" s="78"/>
+      <c r="AQ12" s="97"/>
+      <c r="AR12" s="77"/>
+      <c r="AS12" s="78"/>
+      <c r="AT12" s="78"/>
+      <c r="AU12" s="78"/>
+      <c r="AV12" s="78"/>
+      <c r="AW12" s="97"/>
+      <c r="AX12" s="78"/>
+      <c r="AY12" s="78"/>
+      <c r="AZ12" s="78"/>
+      <c r="BA12" s="78"/>
+      <c r="BB12" s="78"/>
+      <c r="BC12" s="78"/>
+      <c r="BD12" s="78"/>
+      <c r="BE12" s="78"/>
+      <c r="BF12" s="78"/>
+      <c r="BG12" s="97"/>
+      <c r="BH12" s="77"/>
+      <c r="BI12" s="78"/>
+      <c r="BJ12" s="78"/>
+      <c r="BK12" s="78"/>
+      <c r="BL12" s="78"/>
+      <c r="BM12" s="97"/>
+      <c r="BN12" s="102"/>
+      <c r="BO12" s="100"/>
+      <c r="BP12" s="100"/>
+      <c r="BQ12" s="100"/>
+      <c r="BR12" s="100"/>
+      <c r="BS12" s="100"/>
+      <c r="BT12" s="100"/>
+      <c r="BU12" s="101"/>
+      <c r="BV12" s="102"/>
+      <c r="BW12" s="100"/>
+      <c r="BX12" s="100"/>
+      <c r="BY12" s="100"/>
+      <c r="BZ12" s="100"/>
+      <c r="CA12" s="100"/>
+      <c r="CB12" s="100"/>
+      <c r="CC12" s="101"/>
       <c r="CD12" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="CE12" s="71" t="s">
-        <v>263</v>
-      </c>
-      <c r="CF12" s="71"/>
-      <c r="CG12" s="71"/>
+        <v>239</v>
+      </c>
+      <c r="CE12" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="CF12" s="78"/>
+      <c r="CG12" s="78"/>
       <c r="CI12" s="16"/>
       <c r="CJ12" s="16"/>
       <c r="CK12" s="48"/>
       <c r="CL12" s="17"/>
-      <c r="CP12" s="71" t="s">
-        <v>244</v>
-      </c>
-      <c r="CQ12" s="101"/>
-      <c r="CR12" s="101"/>
-      <c r="CS12" s="101"/>
-      <c r="CT12" s="101"/>
-      <c r="CU12" s="101"/>
-      <c r="CV12" s="101"/>
-      <c r="CW12" s="101"/>
-      <c r="DB12" s="80"/>
-      <c r="DC12" s="81"/>
-      <c r="DD12" s="89"/>
-      <c r="DE12" s="89"/>
+      <c r="CP12" s="78" t="s">
+        <v>243</v>
+      </c>
+      <c r="CQ12" s="100"/>
+      <c r="CR12" s="100"/>
+      <c r="CS12" s="100"/>
+      <c r="CT12" s="100"/>
+      <c r="CU12" s="100"/>
+      <c r="CV12" s="100"/>
+      <c r="CW12" s="100"/>
+      <c r="DB12" s="154"/>
+      <c r="DC12" s="155"/>
+      <c r="DD12" s="163"/>
+      <c r="DE12" s="163"/>
       <c r="DF12" s="52"/>
-      <c r="DG12" s="84"/>
+      <c r="DG12" s="158"/>
       <c r="DH12" s="52"/>
       <c r="DI12" s="52"/>
-      <c r="DJ12" s="80"/>
-      <c r="DK12" s="87"/>
-      <c r="DL12" s="87"/>
-      <c r="DM12" s="81"/>
-      <c r="DN12" s="80"/>
-      <c r="DO12" s="87"/>
-      <c r="DP12" s="87"/>
-      <c r="DQ12" s="81"/>
+      <c r="DJ12" s="154"/>
+      <c r="DK12" s="161"/>
+      <c r="DL12" s="161"/>
+      <c r="DM12" s="155"/>
+      <c r="DN12" s="154"/>
+      <c r="DO12" s="161"/>
+      <c r="DP12" s="161"/>
+      <c r="DQ12" s="155"/>
       <c r="DR12" s="16"/>
       <c r="DS12" s="16"/>
       <c r="DT12" s="16"/>
@@ -6346,213 +6346,213 @@
       <c r="EE12" s="16"/>
       <c r="EF12" s="16"/>
       <c r="EG12" s="48"/>
-      <c r="EH12" s="71"/>
-      <c r="EI12" s="71"/>
-      <c r="EJ12" s="71"/>
-      <c r="EK12" s="71"/>
-      <c r="EL12" s="71"/>
-      <c r="EM12" s="71"/>
-      <c r="EN12" s="71"/>
-      <c r="EO12" s="94"/>
-      <c r="EP12" s="93"/>
-      <c r="EQ12" s="71"/>
-      <c r="ER12" s="71"/>
-      <c r="ES12" s="71"/>
-      <c r="ET12" s="71"/>
-      <c r="EU12" s="71"/>
-      <c r="EV12" s="71"/>
-      <c r="EW12" s="94"/>
-      <c r="EX12" s="160" t="s">
+      <c r="EH12" s="78"/>
+      <c r="EI12" s="78"/>
+      <c r="EJ12" s="78"/>
+      <c r="EK12" s="78"/>
+      <c r="EL12" s="78"/>
+      <c r="EM12" s="78"/>
+      <c r="EN12" s="78"/>
+      <c r="EO12" s="97"/>
+      <c r="EP12" s="77"/>
+      <c r="EQ12" s="78"/>
+      <c r="ER12" s="78"/>
+      <c r="ES12" s="78"/>
+      <c r="ET12" s="78"/>
+      <c r="EU12" s="78"/>
+      <c r="EV12" s="78"/>
+      <c r="EW12" s="97"/>
+      <c r="EX12" s="126" t="s">
         <v>207</v>
       </c>
       <c r="EY12" s="17"/>
       <c r="FE12" s="18"/>
-      <c r="FK12" s="111" t="s">
+      <c r="FK12" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="FL12" s="111"/>
-      <c r="FM12" s="111"/>
-      <c r="FN12" s="70"/>
-      <c r="FO12" s="72"/>
-      <c r="FP12" s="70"/>
-      <c r="FQ12" s="71"/>
-      <c r="FR12" s="71"/>
-      <c r="FS12" s="71"/>
-      <c r="FT12" s="71"/>
-      <c r="FU12" s="72"/>
-      <c r="FV12" s="101"/>
-      <c r="FW12" s="101"/>
-      <c r="FX12" s="101"/>
-      <c r="FY12" s="101"/>
-      <c r="FZ12" s="101"/>
-      <c r="GA12" s="102"/>
-      <c r="GB12" s="100"/>
-      <c r="GC12" s="101"/>
-      <c r="GD12" s="101"/>
-      <c r="GE12" s="101"/>
-      <c r="GF12" s="101"/>
-      <c r="GG12" s="102"/>
-      <c r="GH12" s="93"/>
-      <c r="GI12" s="71"/>
-      <c r="GJ12" s="71"/>
-      <c r="GK12" s="71"/>
+      <c r="FL12" s="141"/>
+      <c r="FM12" s="141"/>
+      <c r="FN12" s="143"/>
+      <c r="FO12" s="144"/>
+      <c r="FP12" s="143"/>
+      <c r="FQ12" s="78"/>
+      <c r="FR12" s="78"/>
+      <c r="FS12" s="78"/>
+      <c r="FT12" s="78"/>
+      <c r="FU12" s="144"/>
+      <c r="FV12" s="100"/>
+      <c r="FW12" s="100"/>
+      <c r="FX12" s="100"/>
+      <c r="FY12" s="100"/>
+      <c r="FZ12" s="100"/>
+      <c r="GA12" s="101"/>
+      <c r="GB12" s="102"/>
+      <c r="GC12" s="100"/>
+      <c r="GD12" s="100"/>
+      <c r="GE12" s="100"/>
+      <c r="GF12" s="100"/>
+      <c r="GG12" s="101"/>
+      <c r="GH12" s="77"/>
+      <c r="GI12" s="78"/>
+      <c r="GJ12" s="78"/>
+      <c r="GK12" s="78"/>
       <c r="GL12" t="s">
         <v>193</v>
       </c>
-      <c r="GT12" s="93"/>
-      <c r="GU12" s="71"/>
-      <c r="GV12" s="71"/>
-      <c r="GW12" s="71"/>
-      <c r="GX12" s="71"/>
-      <c r="GY12" s="71"/>
-      <c r="GZ12" s="71"/>
-      <c r="HA12" s="94"/>
-      <c r="HB12" s="93"/>
-      <c r="HC12" s="71"/>
-      <c r="HD12" s="71"/>
-      <c r="HE12" s="71"/>
-      <c r="HF12" s="71"/>
-      <c r="HG12" s="71"/>
-      <c r="HH12" s="71"/>
-      <c r="HI12" s="94"/>
+      <c r="GT12" s="77"/>
+      <c r="GU12" s="78"/>
+      <c r="GV12" s="78"/>
+      <c r="GW12" s="78"/>
+      <c r="GX12" s="78"/>
+      <c r="GY12" s="78"/>
+      <c r="GZ12" s="78"/>
+      <c r="HA12" s="97"/>
+      <c r="HB12" s="77"/>
+      <c r="HC12" s="78"/>
+      <c r="HD12" s="78"/>
+      <c r="HE12" s="78"/>
+      <c r="HF12" s="78"/>
+      <c r="HG12" s="78"/>
+      <c r="HH12" s="78"/>
+      <c r="HI12" s="97"/>
     </row>
     <row r="13" spans="1:217" ht="65.650000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7"/>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="140" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="140" t="s">
         <v>228</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>230</v>
       </c>
       <c r="E13" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F13" s="78" t="s">
         <v>259</v>
       </c>
-      <c r="F13" s="71" t="s">
-        <v>260</v>
-      </c>
-      <c r="G13" s="71"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="101"/>
-      <c r="L13" s="101"/>
-      <c r="M13" s="101"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="101"/>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="93"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="94"/>
-      <c r="U13" s="93"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="94"/>
-      <c r="X13" s="93"/>
-      <c r="Y13" s="71"/>
-      <c r="Z13" s="94"/>
-      <c r="AA13" s="93"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="71"/>
-      <c r="AD13" s="71"/>
-      <c r="AE13" s="71"/>
-      <c r="AF13" s="71"/>
-      <c r="AG13" s="94"/>
-      <c r="AH13" s="93"/>
-      <c r="AI13" s="71"/>
-      <c r="AJ13" s="71"/>
-      <c r="AK13" s="71"/>
-      <c r="AL13" s="71"/>
-      <c r="AM13" s="71"/>
-      <c r="AN13" s="71"/>
-      <c r="AO13" s="71"/>
-      <c r="AP13" s="71"/>
-      <c r="AQ13" s="94"/>
-      <c r="AR13" s="93"/>
-      <c r="AS13" s="71"/>
-      <c r="AT13" s="71"/>
-      <c r="AU13" s="71"/>
-      <c r="AV13" s="71"/>
-      <c r="AW13" s="94"/>
-      <c r="AX13" s="71"/>
-      <c r="AY13" s="71"/>
-      <c r="AZ13" s="71"/>
-      <c r="BA13" s="71"/>
-      <c r="BB13" s="71"/>
-      <c r="BC13" s="71"/>
-      <c r="BD13" s="71"/>
-      <c r="BE13" s="71"/>
-      <c r="BF13" s="71"/>
-      <c r="BG13" s="94"/>
-      <c r="BH13" s="93"/>
-      <c r="BI13" s="71"/>
-      <c r="BJ13" s="71"/>
-      <c r="BK13" s="71"/>
-      <c r="BL13" s="71"/>
-      <c r="BM13" s="94"/>
-      <c r="BN13" s="100"/>
-      <c r="BO13" s="101"/>
-      <c r="BP13" s="101"/>
-      <c r="BQ13" s="101"/>
-      <c r="BR13" s="101"/>
-      <c r="BS13" s="101"/>
-      <c r="BT13" s="101"/>
-      <c r="BU13" s="102"/>
-      <c r="BV13" s="100"/>
-      <c r="BW13" s="101"/>
-      <c r="BX13" s="101"/>
-      <c r="BY13" s="101"/>
-      <c r="BZ13" s="101"/>
-      <c r="CA13" s="101"/>
-      <c r="CB13" s="101"/>
-      <c r="CC13" s="102"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="100"/>
+      <c r="N13" s="100"/>
+      <c r="O13" s="100"/>
+      <c r="P13" s="100"/>
+      <c r="Q13" s="101"/>
+      <c r="R13" s="77"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="97"/>
+      <c r="U13" s="77"/>
+      <c r="V13" s="78"/>
+      <c r="W13" s="97"/>
+      <c r="X13" s="77"/>
+      <c r="Y13" s="78"/>
+      <c r="Z13" s="97"/>
+      <c r="AA13" s="77"/>
+      <c r="AB13" s="78"/>
+      <c r="AC13" s="78"/>
+      <c r="AD13" s="78"/>
+      <c r="AE13" s="78"/>
+      <c r="AF13" s="78"/>
+      <c r="AG13" s="97"/>
+      <c r="AH13" s="77"/>
+      <c r="AI13" s="78"/>
+      <c r="AJ13" s="78"/>
+      <c r="AK13" s="78"/>
+      <c r="AL13" s="78"/>
+      <c r="AM13" s="78"/>
+      <c r="AN13" s="78"/>
+      <c r="AO13" s="78"/>
+      <c r="AP13" s="78"/>
+      <c r="AQ13" s="97"/>
+      <c r="AR13" s="77"/>
+      <c r="AS13" s="78"/>
+      <c r="AT13" s="78"/>
+      <c r="AU13" s="78"/>
+      <c r="AV13" s="78"/>
+      <c r="AW13" s="97"/>
+      <c r="AX13" s="78"/>
+      <c r="AY13" s="78"/>
+      <c r="AZ13" s="78"/>
+      <c r="BA13" s="78"/>
+      <c r="BB13" s="78"/>
+      <c r="BC13" s="78"/>
+      <c r="BD13" s="78"/>
+      <c r="BE13" s="78"/>
+      <c r="BF13" s="78"/>
+      <c r="BG13" s="97"/>
+      <c r="BH13" s="77"/>
+      <c r="BI13" s="78"/>
+      <c r="BJ13" s="78"/>
+      <c r="BK13" s="78"/>
+      <c r="BL13" s="78"/>
+      <c r="BM13" s="97"/>
+      <c r="BN13" s="102"/>
+      <c r="BO13" s="100"/>
+      <c r="BP13" s="100"/>
+      <c r="BQ13" s="100"/>
+      <c r="BR13" s="100"/>
+      <c r="BS13" s="100"/>
+      <c r="BT13" s="100"/>
+      <c r="BU13" s="101"/>
+      <c r="BV13" s="102"/>
+      <c r="BW13" s="100"/>
+      <c r="BX13" s="100"/>
+      <c r="BY13" s="100"/>
+      <c r="BZ13" s="100"/>
+      <c r="CA13" s="100"/>
+      <c r="CB13" s="100"/>
+      <c r="CC13" s="101"/>
       <c r="CD13" s="47" t="s">
-        <v>241</v>
-      </c>
-      <c r="CE13" s="71" t="s">
-        <v>249</v>
-      </c>
-      <c r="CF13" s="71"/>
-      <c r="CG13" s="71"/>
+        <v>240</v>
+      </c>
+      <c r="CE13" s="78" t="s">
+        <v>248</v>
+      </c>
+      <c r="CF13" s="78"/>
+      <c r="CG13" s="78"/>
       <c r="CH13" s="16"/>
       <c r="CI13" s="16"/>
       <c r="CJ13" s="16"/>
       <c r="CK13" s="48"/>
       <c r="CL13" s="17"/>
-      <c r="CP13" s="101"/>
-      <c r="CQ13" s="101"/>
-      <c r="CR13" s="101"/>
-      <c r="CS13" s="101"/>
-      <c r="CT13" s="101"/>
-      <c r="CU13" s="101"/>
-      <c r="CV13" s="101"/>
-      <c r="CW13" s="101"/>
-      <c r="DB13" s="70" t="s">
-        <v>274</v>
-      </c>
-      <c r="DC13" s="71"/>
-      <c r="DD13" s="71"/>
-      <c r="DE13" s="71"/>
-      <c r="DF13" s="71"/>
-      <c r="DG13" s="71"/>
-      <c r="DH13" s="71"/>
-      <c r="DI13" s="71"/>
-      <c r="DJ13" s="71"/>
-      <c r="DK13" s="71"/>
-      <c r="DL13" s="71"/>
-      <c r="DM13" s="71"/>
-      <c r="DN13" s="71"/>
-      <c r="DO13" s="71"/>
-      <c r="DP13" s="71"/>
-      <c r="DQ13" s="72"/>
-      <c r="DR13" s="69" t="s">
+      <c r="CP13" s="100"/>
+      <c r="CQ13" s="100"/>
+      <c r="CR13" s="100"/>
+      <c r="CS13" s="100"/>
+      <c r="CT13" s="100"/>
+      <c r="CU13" s="100"/>
+      <c r="CV13" s="100"/>
+      <c r="CW13" s="100"/>
+      <c r="DB13" s="143" t="s">
+        <v>273</v>
+      </c>
+      <c r="DC13" s="78"/>
+      <c r="DD13" s="78"/>
+      <c r="DE13" s="78"/>
+      <c r="DF13" s="78"/>
+      <c r="DG13" s="78"/>
+      <c r="DH13" s="78"/>
+      <c r="DI13" s="78"/>
+      <c r="DJ13" s="78"/>
+      <c r="DK13" s="78"/>
+      <c r="DL13" s="78"/>
+      <c r="DM13" s="78"/>
+      <c r="DN13" s="78"/>
+      <c r="DO13" s="78"/>
+      <c r="DP13" s="78"/>
+      <c r="DQ13" s="144"/>
+      <c r="DR13" s="140" t="s">
         <v>221</v>
       </c>
-      <c r="DS13" s="69"/>
-      <c r="DT13" s="69"/>
-      <c r="DU13" s="69"/>
+      <c r="DS13" s="140"/>
+      <c r="DT13" s="140"/>
+      <c r="DU13" s="140"/>
       <c r="DV13" s="16"/>
       <c r="DW13" s="16"/>
       <c r="DX13" s="16"/>
@@ -6565,82 +6565,82 @@
       <c r="EE13" s="16"/>
       <c r="EF13" s="16"/>
       <c r="EG13" s="48"/>
-      <c r="EH13" s="71"/>
-      <c r="EI13" s="71"/>
-      <c r="EJ13" s="71"/>
-      <c r="EK13" s="71"/>
-      <c r="EL13" s="71"/>
-      <c r="EM13" s="71"/>
-      <c r="EN13" s="71"/>
-      <c r="EO13" s="94"/>
-      <c r="EP13" s="93"/>
-      <c r="EQ13" s="71"/>
-      <c r="ER13" s="71"/>
-      <c r="ES13" s="71"/>
-      <c r="ET13" s="71"/>
-      <c r="EU13" s="71"/>
-      <c r="EV13" s="71"/>
-      <c r="EW13" s="94"/>
-      <c r="EX13" s="160"/>
+      <c r="EH13" s="78"/>
+      <c r="EI13" s="78"/>
+      <c r="EJ13" s="78"/>
+      <c r="EK13" s="78"/>
+      <c r="EL13" s="78"/>
+      <c r="EM13" s="78"/>
+      <c r="EN13" s="78"/>
+      <c r="EO13" s="97"/>
+      <c r="EP13" s="77"/>
+      <c r="EQ13" s="78"/>
+      <c r="ER13" s="78"/>
+      <c r="ES13" s="78"/>
+      <c r="ET13" s="78"/>
+      <c r="EU13" s="78"/>
+      <c r="EV13" s="78"/>
+      <c r="EW13" s="97"/>
+      <c r="EX13" s="126"/>
       <c r="EY13" s="17" t="s">
         <v>205</v>
       </c>
       <c r="FE13" s="18"/>
-      <c r="FK13" s="115" t="s">
+      <c r="FK13" s="89" t="s">
         <v>214</v>
       </c>
-      <c r="FL13" s="115"/>
-      <c r="FM13" s="117"/>
-      <c r="FN13" s="70"/>
-      <c r="FO13" s="72"/>
-      <c r="FP13" s="70"/>
-      <c r="FQ13" s="71"/>
-      <c r="FR13" s="71"/>
-      <c r="FS13" s="71"/>
-      <c r="FT13" s="71"/>
-      <c r="FU13" s="72"/>
-      <c r="FV13" s="101"/>
-      <c r="FW13" s="101"/>
-      <c r="FX13" s="101"/>
-      <c r="FY13" s="101"/>
-      <c r="FZ13" s="101"/>
-      <c r="GA13" s="102"/>
-      <c r="GB13" s="100"/>
-      <c r="GC13" s="101"/>
-      <c r="GD13" s="101"/>
-      <c r="GE13" s="101"/>
-      <c r="GF13" s="101"/>
-      <c r="GG13" s="102"/>
-      <c r="GH13" s="93"/>
-      <c r="GI13" s="71"/>
-      <c r="GJ13" s="71"/>
-      <c r="GK13" s="71"/>
+      <c r="FL13" s="89"/>
+      <c r="FM13" s="90"/>
+      <c r="FN13" s="143"/>
+      <c r="FO13" s="144"/>
+      <c r="FP13" s="143"/>
+      <c r="FQ13" s="78"/>
+      <c r="FR13" s="78"/>
+      <c r="FS13" s="78"/>
+      <c r="FT13" s="78"/>
+      <c r="FU13" s="144"/>
+      <c r="FV13" s="100"/>
+      <c r="FW13" s="100"/>
+      <c r="FX13" s="100"/>
+      <c r="FY13" s="100"/>
+      <c r="FZ13" s="100"/>
+      <c r="GA13" s="101"/>
+      <c r="GB13" s="102"/>
+      <c r="GC13" s="100"/>
+      <c r="GD13" s="100"/>
+      <c r="GE13" s="100"/>
+      <c r="GF13" s="100"/>
+      <c r="GG13" s="101"/>
+      <c r="GH13" s="77"/>
+      <c r="GI13" s="78"/>
+      <c r="GJ13" s="78"/>
+      <c r="GK13" s="78"/>
       <c r="GN13" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="GT13" s="93"/>
-      <c r="GU13" s="71"/>
-      <c r="GV13" s="71"/>
-      <c r="GW13" s="71"/>
-      <c r="GX13" s="71"/>
-      <c r="GY13" s="71"/>
-      <c r="GZ13" s="71"/>
-      <c r="HA13" s="94"/>
-      <c r="HB13" s="93"/>
-      <c r="HC13" s="71"/>
-      <c r="HD13" s="71"/>
-      <c r="HE13" s="71"/>
-      <c r="HF13" s="71"/>
-      <c r="HG13" s="71"/>
-      <c r="HH13" s="71"/>
-      <c r="HI13" s="94"/>
+      <c r="GT13" s="77"/>
+      <c r="GU13" s="78"/>
+      <c r="GV13" s="78"/>
+      <c r="GW13" s="78"/>
+      <c r="GX13" s="78"/>
+      <c r="GY13" s="78"/>
+      <c r="GZ13" s="78"/>
+      <c r="HA13" s="97"/>
+      <c r="HB13" s="77"/>
+      <c r="HC13" s="78"/>
+      <c r="HD13" s="78"/>
+      <c r="HE13" s="78"/>
+      <c r="HF13" s="78"/>
+      <c r="HG13" s="78"/>
+      <c r="HH13" s="78"/>
+      <c r="HI13" s="97"/>
     </row>
     <row r="14" spans="1:217" ht="77.650000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="7"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
       <c r="D14" s="49" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="49"/>
@@ -6655,54 +6655,54 @@
       <c r="O14" s="104"/>
       <c r="P14" s="104"/>
       <c r="Q14" s="105"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="97"/>
-      <c r="U14" s="95"/>
-      <c r="V14" s="96"/>
-      <c r="W14" s="97"/>
-      <c r="X14" s="95"/>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="97"/>
-      <c r="AA14" s="95"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="96"/>
-      <c r="AE14" s="96"/>
-      <c r="AF14" s="96"/>
-      <c r="AG14" s="97"/>
-      <c r="AH14" s="95"/>
-      <c r="AI14" s="96"/>
-      <c r="AJ14" s="96"/>
-      <c r="AK14" s="96"/>
-      <c r="AL14" s="96"/>
-      <c r="AM14" s="96"/>
-      <c r="AN14" s="96"/>
-      <c r="AO14" s="96"/>
-      <c r="AP14" s="96"/>
-      <c r="AQ14" s="97"/>
-      <c r="AR14" s="95"/>
-      <c r="AS14" s="96"/>
-      <c r="AT14" s="96"/>
-      <c r="AU14" s="96"/>
-      <c r="AV14" s="96"/>
-      <c r="AW14" s="97"/>
-      <c r="AX14" s="96"/>
-      <c r="AY14" s="96"/>
-      <c r="AZ14" s="96"/>
-      <c r="BA14" s="96"/>
-      <c r="BB14" s="96"/>
-      <c r="BC14" s="96"/>
-      <c r="BD14" s="96"/>
-      <c r="BE14" s="96"/>
-      <c r="BF14" s="96"/>
-      <c r="BG14" s="97"/>
-      <c r="BH14" s="95"/>
-      <c r="BI14" s="96"/>
-      <c r="BJ14" s="96"/>
-      <c r="BK14" s="96"/>
-      <c r="BL14" s="96"/>
-      <c r="BM14" s="97"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="119"/>
+      <c r="T14" s="120"/>
+      <c r="U14" s="96"/>
+      <c r="V14" s="119"/>
+      <c r="W14" s="120"/>
+      <c r="X14" s="96"/>
+      <c r="Y14" s="119"/>
+      <c r="Z14" s="120"/>
+      <c r="AA14" s="96"/>
+      <c r="AB14" s="119"/>
+      <c r="AC14" s="119"/>
+      <c r="AD14" s="119"/>
+      <c r="AE14" s="119"/>
+      <c r="AF14" s="119"/>
+      <c r="AG14" s="120"/>
+      <c r="AH14" s="96"/>
+      <c r="AI14" s="119"/>
+      <c r="AJ14" s="119"/>
+      <c r="AK14" s="119"/>
+      <c r="AL14" s="119"/>
+      <c r="AM14" s="119"/>
+      <c r="AN14" s="119"/>
+      <c r="AO14" s="119"/>
+      <c r="AP14" s="119"/>
+      <c r="AQ14" s="120"/>
+      <c r="AR14" s="96"/>
+      <c r="AS14" s="119"/>
+      <c r="AT14" s="119"/>
+      <c r="AU14" s="119"/>
+      <c r="AV14" s="119"/>
+      <c r="AW14" s="120"/>
+      <c r="AX14" s="119"/>
+      <c r="AY14" s="119"/>
+      <c r="AZ14" s="119"/>
+      <c r="BA14" s="119"/>
+      <c r="BB14" s="119"/>
+      <c r="BC14" s="119"/>
+      <c r="BD14" s="119"/>
+      <c r="BE14" s="119"/>
+      <c r="BF14" s="119"/>
+      <c r="BG14" s="120"/>
+      <c r="BH14" s="96"/>
+      <c r="BI14" s="119"/>
+      <c r="BJ14" s="119"/>
+      <c r="BK14" s="119"/>
+      <c r="BL14" s="119"/>
+      <c r="BM14" s="120"/>
       <c r="BN14" s="103"/>
       <c r="BO14" s="104"/>
       <c r="BP14" s="104"/>
@@ -6720,7 +6720,7 @@
       <c r="CB14" s="104"/>
       <c r="CC14" s="105"/>
       <c r="CD14" s="47" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="CE14" s="20"/>
       <c r="CF14" s="20"/>
@@ -6745,28 +6745,28 @@
       <c r="CY14" s="20"/>
       <c r="CZ14" s="20"/>
       <c r="DA14" s="20"/>
-      <c r="DB14" s="73"/>
-      <c r="DC14" s="74"/>
-      <c r="DD14" s="74"/>
-      <c r="DE14" s="74"/>
-      <c r="DF14" s="74"/>
-      <c r="DG14" s="74"/>
-      <c r="DH14" s="74"/>
-      <c r="DI14" s="74"/>
-      <c r="DJ14" s="74"/>
-      <c r="DK14" s="74"/>
-      <c r="DL14" s="74"/>
-      <c r="DM14" s="74"/>
-      <c r="DN14" s="74"/>
-      <c r="DO14" s="74"/>
-      <c r="DP14" s="74"/>
-      <c r="DQ14" s="75"/>
-      <c r="DR14" s="69" t="s">
+      <c r="DB14" s="74"/>
+      <c r="DC14" s="75"/>
+      <c r="DD14" s="75"/>
+      <c r="DE14" s="75"/>
+      <c r="DF14" s="75"/>
+      <c r="DG14" s="75"/>
+      <c r="DH14" s="75"/>
+      <c r="DI14" s="75"/>
+      <c r="DJ14" s="75"/>
+      <c r="DK14" s="75"/>
+      <c r="DL14" s="75"/>
+      <c r="DM14" s="75"/>
+      <c r="DN14" s="75"/>
+      <c r="DO14" s="75"/>
+      <c r="DP14" s="75"/>
+      <c r="DQ14" s="76"/>
+      <c r="DR14" s="140" t="s">
         <v>222</v>
       </c>
-      <c r="DS14" s="69"/>
-      <c r="DT14" s="69"/>
-      <c r="DU14" s="69"/>
+      <c r="DS14" s="140"/>
+      <c r="DT14" s="140"/>
+      <c r="DU14" s="140"/>
       <c r="DV14" s="49"/>
       <c r="DW14" s="49"/>
       <c r="DX14" s="49"/>
@@ -6779,15 +6779,15 @@
       <c r="EE14" s="49"/>
       <c r="EF14" s="49"/>
       <c r="EG14" s="50"/>
-      <c r="EP14" s="95"/>
-      <c r="EQ14" s="96"/>
-      <c r="ER14" s="96"/>
-      <c r="ES14" s="96"/>
-      <c r="ET14" s="96"/>
-      <c r="EU14" s="96"/>
-      <c r="EV14" s="96"/>
-      <c r="EW14" s="97"/>
-      <c r="EX14" s="161"/>
+      <c r="EP14" s="96"/>
+      <c r="EQ14" s="119"/>
+      <c r="ER14" s="119"/>
+      <c r="ES14" s="119"/>
+      <c r="ET14" s="119"/>
+      <c r="EU14" s="119"/>
+      <c r="EV14" s="119"/>
+      <c r="EW14" s="120"/>
+      <c r="EX14" s="94"/>
       <c r="EY14" s="19"/>
       <c r="EZ14" s="20"/>
       <c r="FA14" s="20" t="s">
@@ -6797,19 +6797,19 @@
       <c r="FC14" s="20"/>
       <c r="FD14" s="20"/>
       <c r="FE14" s="21"/>
-      <c r="FK14" s="118" t="s">
+      <c r="FK14" s="146" t="s">
         <v>202</v>
       </c>
-      <c r="FL14" s="118"/>
-      <c r="FM14" s="119"/>
-      <c r="FN14" s="73"/>
-      <c r="FO14" s="75"/>
-      <c r="FP14" s="73"/>
-      <c r="FQ14" s="74"/>
-      <c r="FR14" s="74"/>
-      <c r="FS14" s="74"/>
-      <c r="FT14" s="74"/>
-      <c r="FU14" s="75"/>
+      <c r="FL14" s="146"/>
+      <c r="FM14" s="147"/>
+      <c r="FN14" s="74"/>
+      <c r="FO14" s="76"/>
+      <c r="FP14" s="74"/>
+      <c r="FQ14" s="75"/>
+      <c r="FR14" s="75"/>
+      <c r="FS14" s="75"/>
+      <c r="FT14" s="75"/>
+      <c r="FU14" s="76"/>
       <c r="FV14" s="104"/>
       <c r="FW14" s="104"/>
       <c r="FX14" s="104"/>
@@ -6822,29 +6822,29 @@
       <c r="GE14" s="104"/>
       <c r="GF14" s="104"/>
       <c r="GG14" s="105"/>
-      <c r="GH14" s="163"/>
-      <c r="GI14" s="74"/>
-      <c r="GJ14" s="74"/>
-      <c r="GK14" s="74"/>
+      <c r="GH14" s="79"/>
+      <c r="GI14" s="75"/>
+      <c r="GJ14" s="75"/>
+      <c r="GK14" s="75"/>
       <c r="GM14" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="GT14" s="95"/>
-      <c r="GU14" s="96"/>
-      <c r="GV14" s="96"/>
-      <c r="GW14" s="96"/>
-      <c r="GX14" s="96"/>
-      <c r="GY14" s="96"/>
-      <c r="GZ14" s="96"/>
-      <c r="HA14" s="97"/>
-      <c r="HB14" s="95"/>
-      <c r="HC14" s="96"/>
-      <c r="HD14" s="96"/>
-      <c r="HE14" s="96"/>
-      <c r="HF14" s="96"/>
-      <c r="HG14" s="96"/>
-      <c r="HH14" s="96"/>
-      <c r="HI14" s="97"/>
+      <c r="GT14" s="96"/>
+      <c r="GU14" s="119"/>
+      <c r="GV14" s="119"/>
+      <c r="GW14" s="119"/>
+      <c r="GX14" s="119"/>
+      <c r="GY14" s="119"/>
+      <c r="GZ14" s="119"/>
+      <c r="HA14" s="120"/>
+      <c r="HB14" s="96"/>
+      <c r="HC14" s="119"/>
+      <c r="HD14" s="119"/>
+      <c r="HE14" s="119"/>
+      <c r="HF14" s="119"/>
+      <c r="HG14" s="119"/>
+      <c r="HH14" s="119"/>
+      <c r="HI14" s="120"/>
     </row>
     <row r="15" spans="1:217" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
@@ -6929,16 +6929,16 @@
       <c r="Z16" s="26"/>
       <c r="AA16" s="26"/>
       <c r="AB16" s="26"/>
-      <c r="CD16" s="107" t="s">
+      <c r="CD16" s="138" t="s">
         <v>99</v>
       </c>
-      <c r="CE16" s="108"/>
-      <c r="CF16" s="108"/>
-      <c r="CG16" s="108"/>
-      <c r="CH16" s="108"/>
-      <c r="CI16" s="108"/>
-      <c r="CJ16" s="108"/>
-      <c r="CK16" s="108"/>
+      <c r="CE16" s="139"/>
+      <c r="CF16" s="139"/>
+      <c r="CG16" s="139"/>
+      <c r="CH16" s="139"/>
+      <c r="CI16" s="139"/>
+      <c r="CJ16" s="139"/>
+      <c r="CK16" s="139"/>
       <c r="DE16" t="s">
         <v>167</v>
       </c>
@@ -6973,14 +6973,14 @@
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
-      <c r="CD17" s="108"/>
-      <c r="CE17" s="108"/>
-      <c r="CF17" s="108"/>
-      <c r="CG17" s="108"/>
-      <c r="CH17" s="108"/>
-      <c r="CI17" s="108"/>
-      <c r="CJ17" s="108"/>
-      <c r="CK17" s="108"/>
+      <c r="CD17" s="139"/>
+      <c r="CE17" s="139"/>
+      <c r="CF17" s="139"/>
+      <c r="CG17" s="139"/>
+      <c r="CH17" s="139"/>
+      <c r="CI17" s="139"/>
+      <c r="CJ17" s="139"/>
+      <c r="CK17" s="139"/>
       <c r="DE17" t="s">
         <v>149</v>
       </c>
@@ -7018,14 +7018,14 @@
       <c r="Z18" s="26"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="26"/>
-      <c r="CD18" s="108"/>
-      <c r="CE18" s="108"/>
-      <c r="CF18" s="108"/>
-      <c r="CG18" s="108"/>
-      <c r="CH18" s="108"/>
-      <c r="CI18" s="108"/>
-      <c r="CJ18" s="108"/>
-      <c r="CK18" s="108"/>
+      <c r="CD18" s="139"/>
+      <c r="CE18" s="139"/>
+      <c r="CF18" s="139"/>
+      <c r="CG18" s="139"/>
+      <c r="CH18" s="139"/>
+      <c r="CI18" s="139"/>
+      <c r="CJ18" s="139"/>
+      <c r="CK18" s="139"/>
       <c r="CL18" s="27" t="s">
         <v>141</v>
       </c>
@@ -7063,14 +7063,14 @@
       <c r="Z19" s="26"/>
       <c r="AA19" s="26"/>
       <c r="AB19" s="26"/>
-      <c r="CD19" s="108"/>
-      <c r="CE19" s="108"/>
-      <c r="CF19" s="108"/>
-      <c r="CG19" s="108"/>
-      <c r="CH19" s="108"/>
-      <c r="CI19" s="108"/>
-      <c r="CJ19" s="108"/>
-      <c r="CK19" s="108"/>
+      <c r="CD19" s="139"/>
+      <c r="CE19" s="139"/>
+      <c r="CF19" s="139"/>
+      <c r="CG19" s="139"/>
+      <c r="CH19" s="139"/>
+      <c r="CI19" s="139"/>
+      <c r="CJ19" s="139"/>
+      <c r="CK19" s="139"/>
       <c r="CM19" t="s">
         <v>148</v>
       </c>
@@ -7103,14 +7103,14 @@
       <c r="Z20" s="26"/>
       <c r="AA20" s="26"/>
       <c r="AB20" s="26"/>
-      <c r="CD20" s="108"/>
-      <c r="CE20" s="108"/>
-      <c r="CF20" s="108"/>
-      <c r="CG20" s="108"/>
-      <c r="CH20" s="108"/>
-      <c r="CI20" s="108"/>
-      <c r="CJ20" s="108"/>
-      <c r="CK20" s="108"/>
+      <c r="CD20" s="139"/>
+      <c r="CE20" s="139"/>
+      <c r="CF20" s="139"/>
+      <c r="CG20" s="139"/>
+      <c r="CH20" s="139"/>
+      <c r="CI20" s="139"/>
+      <c r="CJ20" s="139"/>
+      <c r="CK20" s="139"/>
       <c r="DI20" t="s">
         <v>163</v>
       </c>
@@ -7146,14 +7146,14 @@
       <c r="Z21" s="26"/>
       <c r="AA21" s="26"/>
       <c r="AB21" s="26"/>
-      <c r="CD21" s="108"/>
-      <c r="CE21" s="108"/>
-      <c r="CF21" s="108"/>
-      <c r="CG21" s="108"/>
-      <c r="CH21" s="108"/>
-      <c r="CI21" s="108"/>
-      <c r="CJ21" s="108"/>
-      <c r="CK21" s="108"/>
+      <c r="CD21" s="139"/>
+      <c r="CE21" s="139"/>
+      <c r="CF21" s="139"/>
+      <c r="CG21" s="139"/>
+      <c r="CH21" s="139"/>
+      <c r="CI21" s="139"/>
+      <c r="CJ21" s="139"/>
+      <c r="CK21" s="139"/>
       <c r="CL21" t="s">
         <v>151</v>
       </c>
@@ -7204,14 +7204,14 @@
       <c r="Z22" s="26"/>
       <c r="AA22" s="26"/>
       <c r="AB22" s="26"/>
-      <c r="CD22" s="108"/>
-      <c r="CE22" s="108"/>
-      <c r="CF22" s="108"/>
-      <c r="CG22" s="108"/>
-      <c r="CH22" s="108"/>
-      <c r="CI22" s="108"/>
-      <c r="CJ22" s="108"/>
-      <c r="CK22" s="108"/>
+      <c r="CD22" s="139"/>
+      <c r="CE22" s="139"/>
+      <c r="CF22" s="139"/>
+      <c r="CG22" s="139"/>
+      <c r="CH22" s="139"/>
+      <c r="CI22" s="139"/>
+      <c r="CJ22" s="139"/>
+      <c r="CK22" s="139"/>
       <c r="DR22" t="s">
         <v>147</v>
       </c>
@@ -7249,14 +7249,14 @@
       <c r="Z23" s="26"/>
       <c r="AA23" s="26"/>
       <c r="AB23" s="26"/>
-      <c r="CD23" s="108"/>
-      <c r="CE23" s="108"/>
-      <c r="CF23" s="108"/>
-      <c r="CG23" s="108"/>
-      <c r="CH23" s="108"/>
-      <c r="CI23" s="108"/>
-      <c r="CJ23" s="108"/>
-      <c r="CK23" s="108"/>
+      <c r="CD23" s="139"/>
+      <c r="CE23" s="139"/>
+      <c r="CF23" s="139"/>
+      <c r="CG23" s="139"/>
+      <c r="CH23" s="139"/>
+      <c r="CI23" s="139"/>
+      <c r="CJ23" s="139"/>
+      <c r="CK23" s="139"/>
       <c r="DE23" t="s">
         <v>158</v>
       </c>
@@ -7277,14 +7277,14 @@
         <f t="shared" si="41"/>
         <v>5974</v>
       </c>
-      <c r="CD24" s="108"/>
-      <c r="CE24" s="108"/>
-      <c r="CF24" s="108"/>
-      <c r="CG24" s="108"/>
-      <c r="CH24" s="108"/>
-      <c r="CI24" s="108"/>
-      <c r="CJ24" s="108"/>
-      <c r="CK24" s="108"/>
+      <c r="CD24" s="139"/>
+      <c r="CE24" s="139"/>
+      <c r="CF24" s="139"/>
+      <c r="CG24" s="139"/>
+      <c r="CH24" s="139"/>
+      <c r="CI24" s="139"/>
+      <c r="CJ24" s="139"/>
+      <c r="CK24" s="139"/>
       <c r="DG24" t="s">
         <v>159</v>
       </c>
@@ -7305,14 +7305,14 @@
         <f t="shared" si="41"/>
         <v>5975</v>
       </c>
-      <c r="CD25" s="108"/>
-      <c r="CE25" s="108"/>
-      <c r="CF25" s="108"/>
-      <c r="CG25" s="108"/>
-      <c r="CH25" s="108"/>
-      <c r="CI25" s="108"/>
-      <c r="CJ25" s="108"/>
-      <c r="CK25" s="108"/>
+      <c r="CD25" s="139"/>
+      <c r="CE25" s="139"/>
+      <c r="CF25" s="139"/>
+      <c r="CG25" s="139"/>
+      <c r="CH25" s="139"/>
+      <c r="CI25" s="139"/>
+      <c r="CJ25" s="139"/>
+      <c r="CK25" s="139"/>
       <c r="DG25" t="s">
         <v>162</v>
       </c>
@@ -7333,14 +7333,14 @@
         <f t="shared" si="41"/>
         <v>5976</v>
       </c>
-      <c r="CD26" s="108"/>
-      <c r="CE26" s="108"/>
-      <c r="CF26" s="108"/>
-      <c r="CG26" s="108"/>
-      <c r="CH26" s="108"/>
-      <c r="CI26" s="108"/>
-      <c r="CJ26" s="108"/>
-      <c r="CK26" s="108"/>
+      <c r="CD26" s="139"/>
+      <c r="CE26" s="139"/>
+      <c r="CF26" s="139"/>
+      <c r="CG26" s="139"/>
+      <c r="CH26" s="139"/>
+      <c r="CI26" s="139"/>
+      <c r="CJ26" s="139"/>
+      <c r="CK26" s="139"/>
       <c r="DG26" t="s">
         <v>160</v>
       </c>
@@ -7358,14 +7358,14 @@
         <f t="shared" si="41"/>
         <v>5977</v>
       </c>
-      <c r="CD27" s="108"/>
-      <c r="CE27" s="108"/>
-      <c r="CF27" s="108"/>
-      <c r="CG27" s="108"/>
-      <c r="CH27" s="108"/>
-      <c r="CI27" s="108"/>
-      <c r="CJ27" s="108"/>
-      <c r="CK27" s="108"/>
+      <c r="CD27" s="139"/>
+      <c r="CE27" s="139"/>
+      <c r="CF27" s="139"/>
+      <c r="CG27" s="139"/>
+      <c r="CH27" s="139"/>
+      <c r="CI27" s="139"/>
+      <c r="CJ27" s="139"/>
+      <c r="CK27" s="139"/>
       <c r="DG27" t="s">
         <v>161</v>
       </c>
@@ -7383,14 +7383,14 @@
         <f t="shared" si="41"/>
         <v>5978</v>
       </c>
-      <c r="CD28" s="108"/>
-      <c r="CE28" s="108"/>
-      <c r="CF28" s="108"/>
-      <c r="CG28" s="108"/>
-      <c r="CH28" s="108"/>
-      <c r="CI28" s="108"/>
-      <c r="CJ28" s="108"/>
-      <c r="CK28" s="108"/>
+      <c r="CD28" s="139"/>
+      <c r="CE28" s="139"/>
+      <c r="CF28" s="139"/>
+      <c r="CG28" s="139"/>
+      <c r="CH28" s="139"/>
+      <c r="CI28" s="139"/>
+      <c r="CJ28" s="139"/>
+      <c r="CK28" s="139"/>
       <c r="EX28" t="s">
         <v>156</v>
       </c>
@@ -7408,14 +7408,14 @@
         <f t="shared" si="41"/>
         <v>5979</v>
       </c>
-      <c r="CD29" s="108"/>
-      <c r="CE29" s="108"/>
-      <c r="CF29" s="108"/>
-      <c r="CG29" s="108"/>
-      <c r="CH29" s="108"/>
-      <c r="CI29" s="108"/>
-      <c r="CJ29" s="108"/>
-      <c r="CK29" s="108"/>
+      <c r="CD29" s="139"/>
+      <c r="CE29" s="139"/>
+      <c r="CF29" s="139"/>
+      <c r="CG29" s="139"/>
+      <c r="CH29" s="139"/>
+      <c r="CI29" s="139"/>
+      <c r="CJ29" s="139"/>
+      <c r="CK29" s="139"/>
     </row>
     <row r="30" spans="1:204" x14ac:dyDescent="0.45">
       <c r="A30" s="7"/>
@@ -7566,7 +7566,7 @@
         <v>3248</v>
       </c>
       <c r="CD37" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" spans="1:87" x14ac:dyDescent="0.45">
@@ -7780,25 +7780,144 @@
     </row>
   </sheetData>
   <mergeCells count="181">
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="GH9:GK14"/>
-    <mergeCell ref="GL4:GS4"/>
-    <mergeCell ref="GH7:GK7"/>
-    <mergeCell ref="GO7:GS7"/>
-    <mergeCell ref="GL3:GS3"/>
-    <mergeCell ref="GT3:HA3"/>
-    <mergeCell ref="GT4:HA4"/>
-    <mergeCell ref="GV7:HA7"/>
-    <mergeCell ref="GX8:GY8"/>
-    <mergeCell ref="FK13:FM13"/>
-    <mergeCell ref="GM9:GM10"/>
-    <mergeCell ref="GN9:GN10"/>
-    <mergeCell ref="FN9:FN10"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="FF11:FJ11"/>
-    <mergeCell ref="CE11:CG11"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="DB13:DQ14"/>
+    <mergeCell ref="DB9:DC12"/>
+    <mergeCell ref="DG9:DG12"/>
+    <mergeCell ref="DJ9:DM12"/>
+    <mergeCell ref="DN9:DQ12"/>
+    <mergeCell ref="DD9:DD12"/>
+    <mergeCell ref="DE9:DE12"/>
+    <mergeCell ref="R9:T14"/>
+    <mergeCell ref="U9:W14"/>
+    <mergeCell ref="X9:Z14"/>
+    <mergeCell ref="AA9:AG14"/>
+    <mergeCell ref="BV9:CC14"/>
+    <mergeCell ref="AX9:BG14"/>
+    <mergeCell ref="BH9:BM14"/>
+    <mergeCell ref="AR9:AW14"/>
+    <mergeCell ref="AH9:AQ14"/>
+    <mergeCell ref="BN9:BU14"/>
+    <mergeCell ref="CE9:CG9"/>
+    <mergeCell ref="CH9:CK9"/>
+    <mergeCell ref="CE10:CG10"/>
+    <mergeCell ref="CL9:DA11"/>
+    <mergeCell ref="CE13:CG13"/>
+    <mergeCell ref="CD16:CK29"/>
+    <mergeCell ref="GT9:HA14"/>
+    <mergeCell ref="EH11:EO13"/>
+    <mergeCell ref="EH8:EO8"/>
+    <mergeCell ref="HB9:HI14"/>
+    <mergeCell ref="DR13:DU13"/>
+    <mergeCell ref="DR14:DU14"/>
+    <mergeCell ref="FK12:FM12"/>
+    <mergeCell ref="DR9:DU9"/>
+    <mergeCell ref="GO9:GS10"/>
+    <mergeCell ref="EB9:EG10"/>
+    <mergeCell ref="DV9:EA10"/>
+    <mergeCell ref="GL11:GN11"/>
+    <mergeCell ref="GL9:GL10"/>
+    <mergeCell ref="FN11:FO14"/>
+    <mergeCell ref="EX9:FE9"/>
+    <mergeCell ref="FP11:FU14"/>
+    <mergeCell ref="FK9:FM9"/>
+    <mergeCell ref="FK11:FM11"/>
+    <mergeCell ref="FK10:FM10"/>
+    <mergeCell ref="FK14:FM14"/>
+    <mergeCell ref="CP12:CW14"/>
+    <mergeCell ref="CE12:CG12"/>
+    <mergeCell ref="DJ8:DQ8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="Z2:AG2"/>
+    <mergeCell ref="AH2:AO2"/>
+    <mergeCell ref="AP2:AW2"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="AA7:AG7"/>
+    <mergeCell ref="X7:Z7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="R4:AG4"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="Z3:AG3"/>
+    <mergeCell ref="AH3:AO3"/>
+    <mergeCell ref="AP3:AW3"/>
+    <mergeCell ref="CT2:DA2"/>
+    <mergeCell ref="DB2:DI2"/>
+    <mergeCell ref="CD3:CK3"/>
+    <mergeCell ref="CL3:CS3"/>
+    <mergeCell ref="CT3:DA3"/>
+    <mergeCell ref="X8:Z8"/>
+    <mergeCell ref="GD2:GK2"/>
+    <mergeCell ref="CX7:DA7"/>
+    <mergeCell ref="DJ2:DQ2"/>
+    <mergeCell ref="DR2:DY2"/>
+    <mergeCell ref="DZ2:EG2"/>
+    <mergeCell ref="EH2:EO2"/>
+    <mergeCell ref="AX2:BE2"/>
+    <mergeCell ref="BF2:BM2"/>
+    <mergeCell ref="BN2:BU2"/>
+    <mergeCell ref="BV2:CC2"/>
+    <mergeCell ref="CD2:CK2"/>
+    <mergeCell ref="CL2:CS2"/>
+    <mergeCell ref="DR7:DU7"/>
+    <mergeCell ref="FK7:FM7"/>
+    <mergeCell ref="GB7:GG7"/>
+    <mergeCell ref="FV7:GA7"/>
+    <mergeCell ref="FP7:FU7"/>
+    <mergeCell ref="FV4:GK4"/>
+    <mergeCell ref="GL2:GS2"/>
+    <mergeCell ref="GT2:HA2"/>
+    <mergeCell ref="HB2:HI2"/>
+    <mergeCell ref="B1:BM1"/>
+    <mergeCell ref="FF2:FM2"/>
+    <mergeCell ref="FN2:FU2"/>
+    <mergeCell ref="FV2:GC2"/>
+    <mergeCell ref="FF3:FM3"/>
+    <mergeCell ref="FN3:FU3"/>
+    <mergeCell ref="FV3:GC3"/>
+    <mergeCell ref="BN1:HI1"/>
+    <mergeCell ref="DJ3:DQ3"/>
+    <mergeCell ref="DR3:DY3"/>
+    <mergeCell ref="DZ3:EG3"/>
+    <mergeCell ref="EH3:EO3"/>
+    <mergeCell ref="EP3:EW3"/>
+    <mergeCell ref="EX3:FE3"/>
+    <mergeCell ref="BN3:BU3"/>
+    <mergeCell ref="BV3:CC3"/>
+    <mergeCell ref="DB3:DI3"/>
+    <mergeCell ref="EP2:EW2"/>
+    <mergeCell ref="EX2:FE2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="GD3:GK3"/>
+    <mergeCell ref="HB3:HI3"/>
+    <mergeCell ref="AR7:AW7"/>
+    <mergeCell ref="BH7:BM7"/>
+    <mergeCell ref="AX7:BG7"/>
+    <mergeCell ref="BN7:BU7"/>
+    <mergeCell ref="HB4:HI4"/>
+    <mergeCell ref="AH4:AW4"/>
+    <mergeCell ref="AX4:BM4"/>
+    <mergeCell ref="DR4:EG4"/>
+    <mergeCell ref="EP4:EW4"/>
+    <mergeCell ref="EX4:FE4"/>
+    <mergeCell ref="FF4:FM4"/>
+    <mergeCell ref="FN4:FU4"/>
+    <mergeCell ref="EH4:EO4"/>
+    <mergeCell ref="BN4:BU4"/>
+    <mergeCell ref="BV4:CC4"/>
+    <mergeCell ref="CD4:CK4"/>
+    <mergeCell ref="BV7:CC7"/>
+    <mergeCell ref="EY7:FE7"/>
+    <mergeCell ref="CL4:DA4"/>
+    <mergeCell ref="DB4:DQ4"/>
+    <mergeCell ref="EP7:EW7"/>
+    <mergeCell ref="AX3:BE3"/>
+    <mergeCell ref="BF3:BM3"/>
     <mergeCell ref="HB7:HI7"/>
     <mergeCell ref="I9:Q14"/>
     <mergeCell ref="CD7:CK7"/>
@@ -7823,144 +7942,25 @@
     <mergeCell ref="DJ7:DM7"/>
     <mergeCell ref="CH10:CK10"/>
     <mergeCell ref="CH11:CK11"/>
-    <mergeCell ref="HB3:HI3"/>
-    <mergeCell ref="AR7:AW7"/>
-    <mergeCell ref="BH7:BM7"/>
-    <mergeCell ref="AX7:BG7"/>
-    <mergeCell ref="BN7:BU7"/>
-    <mergeCell ref="HB4:HI4"/>
-    <mergeCell ref="AH4:AW4"/>
-    <mergeCell ref="AX4:BM4"/>
-    <mergeCell ref="DR4:EG4"/>
-    <mergeCell ref="EP4:EW4"/>
-    <mergeCell ref="EX4:FE4"/>
-    <mergeCell ref="FF4:FM4"/>
-    <mergeCell ref="FN4:FU4"/>
-    <mergeCell ref="EH4:EO4"/>
-    <mergeCell ref="BN4:BU4"/>
-    <mergeCell ref="BV4:CC4"/>
-    <mergeCell ref="CD4:CK4"/>
-    <mergeCell ref="BV7:CC7"/>
-    <mergeCell ref="EY7:FE7"/>
-    <mergeCell ref="CL4:DA4"/>
-    <mergeCell ref="DB4:DQ4"/>
-    <mergeCell ref="EP7:EW7"/>
-    <mergeCell ref="AX3:BE3"/>
-    <mergeCell ref="BF3:BM3"/>
-    <mergeCell ref="GL2:GS2"/>
-    <mergeCell ref="GT2:HA2"/>
-    <mergeCell ref="HB2:HI2"/>
-    <mergeCell ref="B1:BM1"/>
-    <mergeCell ref="FF2:FM2"/>
-    <mergeCell ref="FN2:FU2"/>
-    <mergeCell ref="FV2:GC2"/>
-    <mergeCell ref="FF3:FM3"/>
-    <mergeCell ref="FN3:FU3"/>
-    <mergeCell ref="FV3:GC3"/>
-    <mergeCell ref="BN1:HI1"/>
-    <mergeCell ref="DJ3:DQ3"/>
-    <mergeCell ref="DR3:DY3"/>
-    <mergeCell ref="DZ3:EG3"/>
-    <mergeCell ref="EH3:EO3"/>
-    <mergeCell ref="EP3:EW3"/>
-    <mergeCell ref="EX3:FE3"/>
-    <mergeCell ref="BN3:BU3"/>
-    <mergeCell ref="BV3:CC3"/>
-    <mergeCell ref="DB3:DI3"/>
-    <mergeCell ref="EP2:EW2"/>
-    <mergeCell ref="EX2:FE2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="GD3:GK3"/>
-    <mergeCell ref="CT2:DA2"/>
-    <mergeCell ref="DB2:DI2"/>
-    <mergeCell ref="CD3:CK3"/>
-    <mergeCell ref="CL3:CS3"/>
-    <mergeCell ref="CT3:DA3"/>
-    <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="GD2:GK2"/>
-    <mergeCell ref="CX7:DA7"/>
-    <mergeCell ref="DJ2:DQ2"/>
-    <mergeCell ref="DR2:DY2"/>
-    <mergeCell ref="DZ2:EG2"/>
-    <mergeCell ref="EH2:EO2"/>
-    <mergeCell ref="AX2:BE2"/>
-    <mergeCell ref="BF2:BM2"/>
-    <mergeCell ref="BN2:BU2"/>
-    <mergeCell ref="BV2:CC2"/>
-    <mergeCell ref="CD2:CK2"/>
-    <mergeCell ref="CL2:CS2"/>
-    <mergeCell ref="DR7:DU7"/>
-    <mergeCell ref="FK7:FM7"/>
-    <mergeCell ref="GB7:GG7"/>
-    <mergeCell ref="FV7:GA7"/>
-    <mergeCell ref="FP7:FU7"/>
-    <mergeCell ref="FV4:GK4"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="Z2:AG2"/>
-    <mergeCell ref="AH2:AO2"/>
-    <mergeCell ref="AP2:AW2"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="AA7:AG7"/>
-    <mergeCell ref="X7:Z7"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="R4:AG4"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="Z3:AG3"/>
-    <mergeCell ref="AH3:AO3"/>
-    <mergeCell ref="AP3:AW3"/>
-    <mergeCell ref="CD16:CK29"/>
-    <mergeCell ref="GT9:HA14"/>
-    <mergeCell ref="EH11:EO13"/>
-    <mergeCell ref="EH8:EO8"/>
-    <mergeCell ref="HB9:HI14"/>
-    <mergeCell ref="DR13:DU13"/>
-    <mergeCell ref="DR14:DU14"/>
-    <mergeCell ref="FK12:FM12"/>
-    <mergeCell ref="DR9:DU9"/>
-    <mergeCell ref="GO9:GS10"/>
-    <mergeCell ref="EB9:EG10"/>
-    <mergeCell ref="DV9:EA10"/>
-    <mergeCell ref="GL11:GN11"/>
-    <mergeCell ref="GL9:GL10"/>
-    <mergeCell ref="FN11:FO14"/>
-    <mergeCell ref="EX9:FE9"/>
-    <mergeCell ref="FP11:FU14"/>
-    <mergeCell ref="FK9:FM9"/>
-    <mergeCell ref="FK11:FM11"/>
-    <mergeCell ref="FK10:FM10"/>
-    <mergeCell ref="FK14:FM14"/>
-    <mergeCell ref="CP12:CW14"/>
-    <mergeCell ref="CE12:CG12"/>
-    <mergeCell ref="DJ8:DQ8"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="DB13:DQ14"/>
-    <mergeCell ref="DB9:DC12"/>
-    <mergeCell ref="DG9:DG12"/>
-    <mergeCell ref="DJ9:DM12"/>
-    <mergeCell ref="DN9:DQ12"/>
-    <mergeCell ref="DD9:DD12"/>
-    <mergeCell ref="DE9:DE12"/>
-    <mergeCell ref="R9:T14"/>
-    <mergeCell ref="U9:W14"/>
-    <mergeCell ref="X9:Z14"/>
-    <mergeCell ref="AA9:AG14"/>
-    <mergeCell ref="BV9:CC14"/>
-    <mergeCell ref="AX9:BG14"/>
-    <mergeCell ref="BH9:BM14"/>
-    <mergeCell ref="AR9:AW14"/>
-    <mergeCell ref="AH9:AQ14"/>
-    <mergeCell ref="BN9:BU14"/>
-    <mergeCell ref="CE9:CG9"/>
-    <mergeCell ref="CH9:CK9"/>
-    <mergeCell ref="CE10:CG10"/>
-    <mergeCell ref="CL9:DA11"/>
-    <mergeCell ref="CE13:CG13"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="GH9:GK14"/>
+    <mergeCell ref="GL4:GS4"/>
+    <mergeCell ref="GH7:GK7"/>
+    <mergeCell ref="GO7:GS7"/>
+    <mergeCell ref="GL3:GS3"/>
+    <mergeCell ref="GT3:HA3"/>
+    <mergeCell ref="GT4:HA4"/>
+    <mergeCell ref="GV7:HA7"/>
+    <mergeCell ref="GX8:GY8"/>
+    <mergeCell ref="FK13:FM13"/>
+    <mergeCell ref="GM9:GM10"/>
+    <mergeCell ref="GN9:GN10"/>
+    <mergeCell ref="FN9:FN10"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="FF11:FJ11"/>
+    <mergeCell ref="CE11:CG11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8428,12 +8428,12 @@
       <c r="C6" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="134" t="s">
+      <c r="D6" s="87" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="136"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="88"/>
       <c r="H6" s="54" t="s">
         <v>170</v>
       </c>
